--- a/Doc/导出配置/Property.xlsx
+++ b/Doc/导出配置/Property.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02871EF-FDBA-4940-B400-8E394E3B44C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32402997-1EFC-4A76-AB8C-C5348A5F396E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
     <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{49DCD200-4CBD-4231-A8D9-A09B77D14AAF}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{46159546-5070-4E28-9D39-5DC24A179D2A}">
       <text>
         <r>
           <rPr>
@@ -53,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{A00BF20F-7451-4480-B947-1615827AFF82}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{D9872385-1D7F-4779-968A-93EF9C111848}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{FCAAA94F-1C14-409F-B00C-85A4358F04AD}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{2514FA65-1773-43E5-A4C9-D3E14AE63198}">
       <text>
         <r>
           <rPr>
@@ -97,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{289E5316-5D6C-4C38-8D10-D39589E39496}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{C3D1A1FC-8B66-49E6-9C97-7A118712C3FD}">
       <text>
         <r>
           <rPr>
@@ -119,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{F4596213-59A7-4BB9-80CF-4AC10D12DE59}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{18F2BF16-9F68-4AB4-A0D0-96343D2FE826}">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{72B6AD54-23F8-4239-AFFC-F16313B7F489}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{870D72C4-9CA3-4AC9-BAC1-992A3074F42E}">
       <text>
         <r>
           <rPr>
@@ -169,7 +169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{E493045F-E4BE-4F4F-93B3-465F06D03AA9}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{0708D3B2-1AE2-4D0D-8729-17F2EFD2EC62}">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{FF030E49-FBDD-41E4-933C-E14E27AE4079}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{2B8303D8-89ED-41AC-88BF-9FADCC18A5DB}">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{16276936-9E6D-41EB-9225-672D3EEA96DA}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{EA8FAFFE-CBB9-4D25-BD7F-4D6CE8889D5A}">
       <text>
         <r>
           <rPr>
@@ -253,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{D027502B-B3D6-4BBC-8978-54C75D5D6734}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{FF41D897-BDF3-4659-93BD-40F60024E871}">
       <text>
         <r>
           <rPr>
@@ -275,7 +275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{37274C88-EBEB-48FE-BE85-DB521F9D14D6}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{95112FC9-D7F6-423D-934C-0922EBCE6B09}">
       <text>
         <r>
           <rPr>
@@ -305,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{7130DC89-345B-4760-B24B-1CDAC17DDBA2}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{D98E28AF-8ECA-4F8B-8E2C-A01A52D307C8}">
       <text>
         <r>
           <rPr>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="263">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -362,10 +362,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>幸运</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -378,10 +374,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Luck</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AtkMin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1236,9 +1228,6 @@
     <t>降低土系抗性</t>
   </si>
   <si>
-    <t>幸运</t>
-  </si>
-  <si>
     <t>#战斗属性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1247,6 +1236,66 @@
   </si>
   <si>
     <t>#经济属性</t>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnergyMax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色经济属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerOther</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色身上的其他经济属性，例如等级，经验之类的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前体力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrentEnergy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前经验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpMax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrentExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1320,31 +1369,6 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1782,6 +1806,31 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1831,30 +1880,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{100E7CEC-1A4F-420D-BB6B-A17035948EBB}" name="Cfg_Property" displayName="Cfg_Property" ref="A1:N64" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{100E7CEC-1A4F-420D-BB6B-A17035948EBB}" name="Cfg_Property" displayName="Cfg_Property" ref="A1:N68" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <tableColumns count="14">
-    <tableColumn id="9" xr3:uid="{3B8FC0A5-6EC5-4336-9DE8-86D6A6C0810E}" name="索引" dataDxfId="0"/>
-    <tableColumn id="1" xr3:uid="{D2FC6B4B-167C-4D9F-B48B-BAE0E7C444DF}" name="id" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{20484817-2F7B-401F-8704-0806FEF34864}" name="分组" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{148AAF50-6A90-4D77-975D-AB72C9AFC2AE}" name="枚举名称" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{AE80ADAC-C7BC-4C90-AC4D-0BEBDC113A66}" name="显示名称" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{71BC1DB2-3212-4E16-9DA1-CAC4E9A2C703}" name="显示颜色" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{8FC3DA60-6EB6-4A41-92F4-64A603771123}" name="初始化值" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{A8DFE4DC-904B-4A48-B0DE-02121CDF601A}" name="显示生效值" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{3D21E091-3B8A-4981-B66D-61F08BF9B26E}" name="显示格式" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{1F161CC3-AE6E-44AA-A037-5BC87DB68766}" name="下限" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{5A8819C0-D545-4145-AD31-8C5065653BF2}" name="超下限处理" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{B7EF07F4-8703-4CC1-A643-BEAF7A9C5FA0}" name="上限" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{50798A1B-D983-4C28-B229-FDAED6D7A07D}" name="超上限处理" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{C5668DDF-9894-4882-8255-FDABFC97BF72}" name="属性描述" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{3B8FC0A5-6EC5-4336-9DE8-86D6A6C0810E}" name="索引" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{D2FC6B4B-167C-4D9F-B48B-BAE0E7C444DF}" name="id" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{20484817-2F7B-401F-8704-0806FEF34864}" name="分组" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{148AAF50-6A90-4D77-975D-AB72C9AFC2AE}" name="枚举名称" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{AE80ADAC-C7BC-4C90-AC4D-0BEBDC113A66}" name="显示名称" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{71BC1DB2-3212-4E16-9DA1-CAC4E9A2C703}" name="显示颜色" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{8FC3DA60-6EB6-4A41-92F4-64A603771123}" name="初始化值" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{A8DFE4DC-904B-4A48-B0DE-02121CDF601A}" name="显示生效值" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{3D21E091-3B8A-4981-B66D-61F08BF9B26E}" name="显示格式" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{1F161CC3-AE6E-44AA-A037-5BC87DB68766}" name="下限" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{5A8819C0-D545-4145-AD31-8C5065653BF2}" name="超下限处理" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{B7EF07F4-8703-4CC1-A643-BEAF7A9C5FA0}" name="上限" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{50798A1B-D983-4C28-B229-FDAED6D7A07D}" name="超上限处理" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{C5668DDF-9894-4882-8255-FDABFC97BF72}" name="属性描述" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}" name="辅助_属性分组" displayName="辅助_属性分组" ref="A1:E3" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
-  <autoFilter ref="A1:E3" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}" name="辅助_属性分组" displayName="辅助_属性分组" ref="A1:E4" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E4" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -1862,11 +1911,11 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5D6A6F7-AAEC-489A-A982-D454642B9FB1}" name="索引" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{64C8F804-50F6-453C-95D2-735F62062283}" name="类名" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{9D653032-0D75-4239-958F-585FB5B3B1A7}" name="文件名" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{880DFEEF-A9D1-4BEB-8228-F611FA9F52BE}" name="数据分组" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{9F3931FC-0C41-47C2-A9BF-7D7FCD2BDFD8}" name="说明" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{B5D6A6F7-AAEC-489A-A982-D454642B9FB1}" name="索引" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{64C8F804-50F6-453C-95D2-735F62062283}" name="类名" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{9D653032-0D75-4239-958F-585FB5B3B1A7}" name="文件名" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{880DFEEF-A9D1-4BEB-8228-F611FA9F52BE}" name="数据分组" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{9F3931FC-0C41-47C2-A9BF-7D7FCD2BDFD8}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2170,7 +2219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2183,7 +2232,7 @@
     <col min="10" max="10" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="57.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="1"/>
     <col min="15" max="15" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
@@ -2191,13 +2240,13 @@
   <sheetData>
     <row r="1" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -2206,99 +2255,78 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="3"/>
+      <c r="A2" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B3" s="3"/>
+      <c r="A3" s="1" t="s">
+        <v>245</v>
+      </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="3"/>
     </row>
     <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B4" s="3"/>
+      <c r="A4" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="3"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="3"/>
     </row>
     <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>195</v>
+      <c r="A5" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>2</v>
@@ -2308,21 +2336,21 @@
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>196</v>
+      <c r="A6" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
@@ -2332,133 +2360,133 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>197</v>
+      <c r="A7" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G7" s="1">
         <v>10000</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>198</v>
+      <c r="A8" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="B8" s="1">
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G8" s="1">
         <v>8000</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>199</v>
+      <c r="A9" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="B9" s="1">
         <v>100</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="G9" s="1">
         <v>200</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>200</v>
+      <c r="A10" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="B10" s="1">
         <v>101</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="G10" s="1">
         <v>300</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>201</v>
+      <c r="A11" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="B11" s="1">
         <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -2468,24 +2496,24 @@
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>202</v>
+      <c r="A12" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B12" s="1">
         <v>104</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G12" s="1">
         <v>5000</v>
@@ -2494,31 +2522,31 @@
         <v>10000</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L12" s="1">
         <v>9000</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>203</v>
+      <c r="A13" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="B13" s="1">
         <v>105</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G13" s="1">
         <v>15000</v>
@@ -2527,28 +2555,28 @@
         <v>10000</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>204</v>
+      <c r="A14" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="B14" s="1">
         <v>106</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1">
         <v>6000</v>
@@ -2557,103 +2585,103 @@
         <v>10000</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L14" s="1">
         <v>9000</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>205</v>
+      <c r="A15" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="B15" s="1">
         <v>107</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>206</v>
+      <c r="A16" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="B16" s="1">
         <v>200</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>207</v>
+      <c r="A17" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="B17" s="1">
         <v>201</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>208</v>
+      <c r="A18" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="B18" s="1">
         <v>202</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G18" s="1">
         <v>300</v>
@@ -2662,28 +2690,28 @@
         <v>10000</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>209</v>
+      <c r="A19" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="B19" s="1">
         <v>203</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G19" s="1">
         <v>100</v>
@@ -2692,124 +2720,124 @@
         <v>10000</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>210</v>
+      <c r="A20" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="B20" s="1">
         <v>300</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G20" s="1">
         <v>10000</v>
       </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>211</v>
+      <c r="A21" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="B21" s="1">
         <v>301</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G21" s="1">
         <v>5000</v>
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>212</v>
+      <c r="A22" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="B22" s="1">
         <v>400</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G22" s="1">
         <v>1000</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>213</v>
+      <c r="A23" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="B23" s="1">
         <v>401</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G23" s="1">
         <v>200</v>
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>214</v>
+      <c r="A24" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="B24" s="1">
         <v>402</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G24" s="1">
         <v>15000</v>
@@ -2818,52 +2846,52 @@
         <v>10000</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>215</v>
+      <c r="A25" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="B25" s="1">
         <v>500</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G25" s="1">
         <v>15</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
-        <v>216</v>
+      <c r="A26" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="B26" s="1">
         <v>501</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G26" s="1">
         <v>300</v>
@@ -2872,52 +2900,52 @@
         <v>10000</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>217</v>
+      <c r="A27" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="B27" s="1">
         <v>502</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G27" s="1">
         <v>10</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>218</v>
+      <c r="A28" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="B28" s="1">
         <v>503</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G28" s="1">
         <v>200</v>
@@ -2926,52 +2954,52 @@
         <v>10000</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>219</v>
+      <c r="A29" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="B29" s="1">
         <v>508</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G29" s="1">
         <v>15</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>220</v>
+      <c r="A30" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="B30" s="1">
         <v>509</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G30" s="1">
         <v>300</v>
@@ -2980,52 +3008,52 @@
         <v>10000</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>221</v>
+      <c r="A31" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="B31" s="1">
         <v>510</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G31" s="1">
         <v>10</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>222</v>
+      <c r="A32" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="B32" s="1">
         <v>511</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G32" s="1">
         <v>200</v>
@@ -3034,52 +3062,52 @@
         <v>10000</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
-        <v>223</v>
+      <c r="A33" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="B33" s="1">
         <v>600</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G33" s="1">
         <v>19</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>224</v>
+      <c r="A34" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B34" s="1">
         <v>601</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G34" s="1">
         <v>100</v>
@@ -3088,52 +3116,52 @@
         <v>10000</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
-        <v>225</v>
+      <c r="A35" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="B35" s="1">
         <v>602</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G35" s="1">
         <v>50</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>226</v>
+      <c r="A36" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="B36" s="1">
         <v>603</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G36" s="1">
         <v>200</v>
@@ -3142,28 +3170,28 @@
         <v>10000</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>227</v>
+      <c r="A37" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="B37" s="1">
         <v>700</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G37" s="1">
         <v>10000</v>
@@ -3172,28 +3200,28 @@
         <v>10000</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>228</v>
+      <c r="A38" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="B38" s="1">
         <v>701</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G38" s="1">
         <v>1500</v>
@@ -3202,31 +3230,31 @@
         <v>10000</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L38" s="1">
         <v>7500</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>229</v>
+      <c r="A39" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="B39" s="1">
         <v>702</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G39" s="1">
         <v>500</v>
@@ -3235,31 +3263,31 @@
         <v>10000</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L39" s="1">
         <v>2000</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>230</v>
+      <c r="A40" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="B40" s="1">
         <v>703</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G40" s="1">
         <v>200</v>
@@ -3268,28 +3296,28 @@
         <v>10000</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>231</v>
+      <c r="A41" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="B41" s="1">
         <v>800</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G41" s="1">
         <v>10000</v>
@@ -3298,28 +3326,28 @@
         <v>10000</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>232</v>
+      <c r="A42" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="B42" s="1">
         <v>801</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G42" s="1">
         <v>500</v>
@@ -3328,31 +3356,31 @@
         <v>10000</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L42" s="1">
         <v>7500</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>233</v>
+      <c r="A43" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="B43" s="1">
         <v>802</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G43" s="1">
         <v>500</v>
@@ -3361,31 +3389,31 @@
         <v>10000</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L43" s="1">
         <v>2000</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>234</v>
+      <c r="A44" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="B44" s="1">
         <v>803</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G44" s="1">
         <v>300</v>
@@ -3394,28 +3422,28 @@
         <v>10000</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>235</v>
+      <c r="A45" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="B45" s="1">
         <v>900</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G45" s="1">
         <v>10000</v>
@@ -3424,28 +3452,28 @@
         <v>10000</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>236</v>
+      <c r="A46" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="B46" s="1">
         <v>901</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G46" s="1">
         <v>500</v>
@@ -3454,31 +3482,31 @@
         <v>10000</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L46" s="1">
         <v>7500</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>121</v>
+      <c r="A47" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="B47" s="1">
         <v>902</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G47" s="1">
         <v>500</v>
@@ -3487,31 +3515,31 @@
         <v>10000</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L47" s="1">
         <v>2000</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>237</v>
+      <c r="A48" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="B48" s="1">
         <v>903</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G48" s="1">
         <v>300</v>
@@ -3520,28 +3548,28 @@
         <v>10000</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>238</v>
+      <c r="A49" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="B49" s="1">
         <v>1000</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G49" s="1">
         <v>10000</v>
@@ -3550,28 +3578,28 @@
         <v>10000</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>239</v>
+      <c r="A50" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="B50" s="1">
         <v>1001</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G50" s="1">
         <v>500</v>
@@ -3580,31 +3608,31 @@
         <v>10000</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L50" s="1">
         <v>7500</v>
       </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>124</v>
+      <c r="A51" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="B51" s="1">
         <v>1002</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G51" s="1">
         <v>500</v>
@@ -3613,31 +3641,31 @@
         <v>10000</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L51" s="1">
         <v>2000</v>
       </c>
       <c r="M51" s="1"/>
       <c r="N51" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
-        <v>240</v>
+      <c r="A52" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="B52" s="1">
         <v>1003</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G52" s="1">
         <v>300</v>
@@ -3646,28 +3674,28 @@
         <v>10000</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
-        <v>241</v>
+      <c r="A53" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="B53" s="1">
         <v>1100</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G53" s="1">
         <v>10000</v>
@@ -3676,28 +3704,28 @@
         <v>10000</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
-        <v>242</v>
+      <c r="A54" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="B54" s="1">
         <v>1101</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G54" s="1">
         <v>500</v>
@@ -3706,31 +3734,31 @@
         <v>10000</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L54" s="1">
         <v>7500</v>
       </c>
       <c r="M54" s="1"/>
       <c r="N54" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
-        <v>127</v>
+      <c r="A55" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="B55" s="1">
         <v>1102</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G55" s="1">
         <v>500</v>
@@ -3739,31 +3767,31 @@
         <v>10000</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L55" s="1">
         <v>2000</v>
       </c>
       <c r="M55" s="1"/>
       <c r="N55" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
-        <v>243</v>
+      <c r="A56" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="B56" s="1">
         <v>1103</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G56" s="1">
         <v>300</v>
@@ -3772,28 +3800,28 @@
         <v>10000</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
-        <v>244</v>
+      <c r="A57" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="B57" s="1">
         <v>1200</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G57" s="1">
         <v>10000</v>
@@ -3802,28 +3830,28 @@
         <v>10000</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
-        <v>245</v>
+      <c r="A58" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="B58" s="1">
         <v>1201</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G58" s="1">
         <v>500</v>
@@ -3832,31 +3860,31 @@
         <v>10000</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L58" s="1">
         <v>7500</v>
       </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
-        <v>130</v>
+      <c r="A59" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="B59" s="1">
         <v>1202</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G59" s="1">
         <v>500</v>
@@ -3865,31 +3893,31 @@
         <v>10000</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L59" s="1">
         <v>2000</v>
       </c>
       <c r="M59" s="1"/>
       <c r="N59" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="3" t="s">
-        <v>246</v>
+      <c r="A60" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="B60" s="1">
         <v>1203</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G60" s="1">
         <v>300</v>
@@ -3898,16 +3926,16 @@
         <v>10000</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="3" t="s">
-        <v>249</v>
+      <c r="A61" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3924,8 +3952,8 @@
       <c r="N61" s="2"/>
     </row>
     <row r="62" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
-        <v>250</v>
+      <c r="A62" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3942,8 +3970,8 @@
       <c r="N62" s="2"/>
     </row>
     <row r="63" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
-        <v>249</v>
+      <c r="A63" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3960,27 +3988,157 @@
       <c r="N63" s="2"/>
     </row>
     <row r="64" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
-        <v>247</v>
+      <c r="A64" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="B64" s="1">
         <v>10000</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>11</v>
+        <v>250</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M64" s="1"/>
+        <v>248</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L64" s="1">
+        <v>100</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B65" s="3">
+        <v>10001</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3">
+        <v>0</v>
+      </c>
+      <c r="K65" s="2"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B66" s="3">
+        <v>10002</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3">
+        <v>100</v>
+      </c>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B67" s="3">
+        <v>10010</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3">
+        <v>100</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="L67" s="3"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B68" s="3">
+        <v>10011</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3">
+        <v>100</v>
+      </c>
+      <c r="K68" s="2"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="3" t="s">
+        <v>252</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K64 M2:M64" xr:uid="{11F726DE-414D-4E38-91AF-619AA5CC235A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K68 M2:M68" xr:uid="{11F726DE-414D-4E38-91AF-619AA5CC235A}">
       <formula1>"成功,失败,设置为限制"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3995,61 +4153,79 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE678690-F593-430F-863F-9C7548EB1957}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/Doc/导出配置/Property.xlsx
+++ b/Doc/导出配置/Property.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32402997-1EFC-4A76-AB8C-C5348A5F396E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4181F4A2-B5F7-4C5F-86DF-B49DCA57B0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Property" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{46159546-5070-4E28-9D39-5DC24A179D2A}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{3A827A20-9304-4978-B09C-3439D1BB87A9}">
       <text>
         <r>
           <rPr>
@@ -53,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{D9872385-1D7F-4779-968A-93EF9C111848}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{A9966EDB-4519-4B4B-9899-8BB386DDBE1F}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{2514FA65-1773-43E5-A4C9-D3E14AE63198}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{BF74C365-98DD-4059-87A9-7408D6062A0C}">
       <text>
         <r>
           <rPr>
@@ -97,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{C3D1A1FC-8B66-49E6-9C97-7A118712C3FD}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{15430E84-FB46-4FA5-A588-B1D86F7DF686}">
       <text>
         <r>
           <rPr>
@@ -119,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{18F2BF16-9F68-4AB4-A0D0-96343D2FE826}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{E33C43D3-6A5A-4B74-ACDB-219F3A7FD4D9}">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{870D72C4-9CA3-4AC9-BAC1-992A3074F42E}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{AC23F202-6811-4EBC-8C75-166497ABD4FF}">
       <text>
         <r>
           <rPr>
@@ -169,7 +169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{0708D3B2-1AE2-4D0D-8729-17F2EFD2EC62}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{1682EE0B-7565-4965-965B-C23B3976DDBB}">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{2B8303D8-89ED-41AC-88BF-9FADCC18A5DB}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{B33F6634-C818-4355-8FA9-12A6D7E26287}">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{EA8FAFFE-CBB9-4D25-BD7F-4D6CE8889D5A}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{3BE7FBD3-91AB-4D32-B360-830F69191CD5}">
       <text>
         <r>
           <rPr>
@@ -253,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{FF41D897-BDF3-4659-93BD-40F60024E871}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{82B24431-EA23-4577-AC95-F95DDD7847B9}">
       <text>
         <r>
           <rPr>
@@ -275,7 +275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{95112FC9-D7F6-423D-934C-0922EBCE6B09}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{E14A25B6-A31C-4AF0-A63C-76733794AC37}">
       <text>
         <r>
           <rPr>
@@ -305,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{D98E28AF-8ECA-4F8B-8E2C-A01A52D307C8}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{6E11A721-B664-40D3-85DD-BC88155953E5}">
       <text>
         <r>
           <rPr>
@@ -1045,10 +1045,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Fighting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Battle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1266,10 +1262,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PlayerOther</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>角色身上的其他经济属性，例如等级，经验之类的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1295,6 +1287,14 @@
   </si>
   <si>
     <t>CurrentExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fight</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1359,11 +1359,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2284,7 +2283,7 @@
     </row>
     <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C2" s="2"/>
       <c r="H2" s="2"/>
@@ -2295,7 +2294,7 @@
     </row>
     <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2"/>
       <c r="H3" s="2"/>
@@ -2306,7 +2305,7 @@
     </row>
     <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C4" s="2"/>
       <c r="H4" s="2"/>
@@ -2317,7 +2316,7 @@
     </row>
     <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -2341,7 +2340,7 @@
     </row>
     <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2365,7 +2364,7 @@
     </row>
     <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
@@ -2397,7 +2396,7 @@
     </row>
     <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B8" s="1">
         <v>11</v>
@@ -2418,7 +2417,7 @@
         <v>8000</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>181</v>
@@ -2429,7 +2428,7 @@
     </row>
     <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B9" s="1">
         <v>100</v>
@@ -2453,7 +2452,7 @@
     </row>
     <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B10" s="1">
         <v>101</v>
@@ -2477,7 +2476,7 @@
     </row>
     <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B11" s="1">
         <v>103</v>
@@ -2501,7 +2500,7 @@
     </row>
     <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B12" s="1">
         <v>104</v>
@@ -2534,7 +2533,7 @@
     </row>
     <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13" s="1">
         <v>105</v>
@@ -2564,7 +2563,7 @@
     </row>
     <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B14" s="1">
         <v>106</v>
@@ -2597,7 +2596,7 @@
     </row>
     <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B15" s="1">
         <v>107</v>
@@ -2621,7 +2620,7 @@
     </row>
     <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B16" s="1">
         <v>200</v>
@@ -2645,7 +2644,7 @@
     </row>
     <row r="17" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B17" s="1">
         <v>201</v>
@@ -2669,7 +2668,7 @@
     </row>
     <row r="18" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B18" s="1">
         <v>202</v>
@@ -2699,7 +2698,7 @@
     </row>
     <row r="19" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" s="1">
         <v>203</v>
@@ -2729,7 +2728,7 @@
     </row>
     <row r="20" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B20" s="1">
         <v>300</v>
@@ -2753,7 +2752,7 @@
     </row>
     <row r="21" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B21" s="1">
         <v>301</v>
@@ -2777,7 +2776,7 @@
     </row>
     <row r="22" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B22" s="1">
         <v>400</v>
@@ -2801,7 +2800,7 @@
     </row>
     <row r="23" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B23" s="1">
         <v>401</v>
@@ -2825,7 +2824,7 @@
     </row>
     <row r="24" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B24" s="1">
         <v>402</v>
@@ -2855,7 +2854,7 @@
     </row>
     <row r="25" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B25" s="1">
         <v>500</v>
@@ -2879,7 +2878,7 @@
     </row>
     <row r="26" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B26" s="1">
         <v>501</v>
@@ -2909,7 +2908,7 @@
     </row>
     <row r="27" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B27" s="1">
         <v>502</v>
@@ -2933,7 +2932,7 @@
     </row>
     <row r="28" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B28" s="1">
         <v>503</v>
@@ -2963,7 +2962,7 @@
     </row>
     <row r="29" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B29" s="1">
         <v>508</v>
@@ -2987,7 +2986,7 @@
     </row>
     <row r="30" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B30" s="1">
         <v>509</v>
@@ -3017,7 +3016,7 @@
     </row>
     <row r="31" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B31" s="1">
         <v>510</v>
@@ -3041,7 +3040,7 @@
     </row>
     <row r="32" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B32" s="1">
         <v>511</v>
@@ -3071,7 +3070,7 @@
     </row>
     <row r="33" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B33" s="1">
         <v>600</v>
@@ -3095,7 +3094,7 @@
     </row>
     <row r="34" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B34" s="1">
         <v>601</v>
@@ -3125,7 +3124,7 @@
     </row>
     <row r="35" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B35" s="1">
         <v>602</v>
@@ -3149,7 +3148,7 @@
     </row>
     <row r="36" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B36" s="1">
         <v>603</v>
@@ -3179,7 +3178,7 @@
     </row>
     <row r="37" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B37" s="1">
         <v>700</v>
@@ -3209,7 +3208,7 @@
     </row>
     <row r="38" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B38" s="1">
         <v>701</v>
@@ -3242,7 +3241,7 @@
     </row>
     <row r="39" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B39" s="1">
         <v>702</v>
@@ -3275,7 +3274,7 @@
     </row>
     <row r="40" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B40" s="1">
         <v>703</v>
@@ -3305,7 +3304,7 @@
     </row>
     <row r="41" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B41" s="1">
         <v>800</v>
@@ -3335,7 +3334,7 @@
     </row>
     <row r="42" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B42" s="1">
         <v>801</v>
@@ -3368,7 +3367,7 @@
     </row>
     <row r="43" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B43" s="1">
         <v>802</v>
@@ -3401,7 +3400,7 @@
     </row>
     <row r="44" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B44" s="1">
         <v>803</v>
@@ -3431,7 +3430,7 @@
     </row>
     <row r="45" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B45" s="1">
         <v>900</v>
@@ -3461,7 +3460,7 @@
     </row>
     <row r="46" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B46" s="1">
         <v>901</v>
@@ -3527,7 +3526,7 @@
     </row>
     <row r="48" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B48" s="1">
         <v>903</v>
@@ -3557,7 +3556,7 @@
     </row>
     <row r="49" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B49" s="1">
         <v>1000</v>
@@ -3587,7 +3586,7 @@
     </row>
     <row r="50" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B50" s="1">
         <v>1001</v>
@@ -3653,7 +3652,7 @@
     </row>
     <row r="52" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B52" s="1">
         <v>1003</v>
@@ -3683,7 +3682,7 @@
     </row>
     <row r="53" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B53" s="1">
         <v>1100</v>
@@ -3713,7 +3712,7 @@
     </row>
     <row r="54" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B54" s="1">
         <v>1101</v>
@@ -3779,7 +3778,7 @@
     </row>
     <row r="56" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B56" s="1">
         <v>1103</v>
@@ -3809,7 +3808,7 @@
     </row>
     <row r="57" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B57" s="1">
         <v>1200</v>
@@ -3839,7 +3838,7 @@
     </row>
     <row r="58" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B58" s="1">
         <v>1201</v>
@@ -3905,7 +3904,7 @@
     </row>
     <row r="60" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B60" s="1">
         <v>1203</v>
@@ -3935,7 +3934,7 @@
     </row>
     <row r="61" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3953,7 +3952,7 @@
     </row>
     <row r="62" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3971,7 +3970,7 @@
     </row>
     <row r="63" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3989,7 +3988,7 @@
     </row>
     <row r="64" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B64" s="1">
         <v>10000</v>
@@ -3998,10 +3997,10 @@
         <v>178</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -4019,120 +4018,112 @@
         <v>181</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B65" s="3">
+      <c r="A65" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B65" s="1">
         <v>10001</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3">
+      <c r="D65" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G65" s="1">
         <v>0</v>
       </c>
       <c r="K65" s="2"/>
-      <c r="L65" s="3"/>
       <c r="M65" s="2"/>
-      <c r="N65" s="3" t="s">
-        <v>249</v>
+      <c r="N65" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B66" s="3">
+      <c r="A66" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B66" s="1">
         <v>10002</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3">
+      <c r="D66" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G66" s="1">
         <v>100</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="3"/>
       <c r="M66" s="2"/>
-      <c r="N66" s="3" t="s">
-        <v>260</v>
+      <c r="N66" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B67" s="3">
+      <c r="A67" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B67" s="1">
         <v>10010</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="D67" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="G67" s="1">
+        <v>100</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="M67" s="2"/>
+      <c r="N67" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3">
-        <v>100</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="L67" s="3"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B68" s="3">
+      <c r="B68" s="1">
         <v>10011</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E68" s="3" t="s">
+      <c r="D68" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3">
+      <c r="E68" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G68" s="1">
         <v>100</v>
       </c>
       <c r="K68" s="2"/>
-      <c r="L68" s="3"/>
       <c r="M68" s="2"/>
-      <c r="N68" s="3" t="s">
-        <v>252</v>
+      <c r="N68" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4174,7 +4165,7 @@
         <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -4182,16 +4173,16 @@
         <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>186</v>
+        <v>262</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>186</v>
+        <v>262</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>184</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4199,33 +4190,33 @@
         <v>185</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>185</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/Doc/导出配置/Property.xlsx
+++ b/Doc/导出配置/Property.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4181F4A2-B5F7-4C5F-86DF-B49DCA57B0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D8971D-9500-4918-BD3F-3A33BE54E129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Property" sheetId="1" r:id="rId1"/>
     <sheet name="属性代码生成辅助" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,10 +28,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{3A827A20-9304-4978-B09C-3439D1BB87A9}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{535E16FE-F9D1-4379-B289-45475BD76D47}">
       <text>
         <r>
           <rPr>
@@ -39,7 +39,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -53,7 +52,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{A9966EDB-4519-4B4B-9899-8BB386DDBE1F}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{6AC236AF-626A-45A4-8668-9D4295DE37B4}">
       <text>
         <r>
           <rPr>
@@ -61,7 +60,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -75,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{BF74C365-98DD-4059-87A9-7408D6062A0C}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{104C4A92-F3EC-46D7-B534-FFE87E09B7E2}">
       <text>
         <r>
           <rPr>
@@ -83,7 +81,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -97,7 +94,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{15430E84-FB46-4FA5-A588-B1D86F7DF686}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{C42884F1-81AA-453A-ABB4-5314744E0D05}">
       <text>
         <r>
           <rPr>
@@ -105,7 +102,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -119,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{E33C43D3-6A5A-4B74-ACDB-219F3A7FD4D9}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{E5782A8D-40AE-4688-BD9F-90B0A7679BE3}">
       <text>
         <r>
           <rPr>
@@ -127,7 +123,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -143,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{AC23F202-6811-4EBC-8C75-166497ABD4FF}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{DDAEF253-F36A-435B-8186-041D9D643D2C}">
       <text>
         <r>
           <rPr>
@@ -151,7 +146,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -169,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{1682EE0B-7565-4965-965B-C23B3976DDBB}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{5172AE4C-84F6-4977-9DD4-839ECB2375C9}">
       <text>
         <r>
           <rPr>
@@ -177,7 +171,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -199,7 +192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{B33F6634-C818-4355-8FA9-12A6D7E26287}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{446BDA3C-772B-4575-B8D0-8180CD7C1323}">
       <text>
         <r>
           <rPr>
@@ -207,7 +200,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -223,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{3BE7FBD3-91AB-4D32-B360-830F69191CD5}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{14A0C3AF-459C-430F-8A00-8FA8545B232F}">
       <text>
         <r>
           <rPr>
@@ -231,7 +223,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">【字段名】：
@@ -253,7 +244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{82B24431-EA23-4577-AC95-F95DDD7847B9}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{C84B1BC0-BFF0-4871-AA07-901CF64EA536}">
       <text>
         <r>
           <rPr>
@@ -261,7 +252,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -275,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{E14A25B6-A31C-4AF0-A63C-76733794AC37}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{30EF11FE-175F-481D-B621-8C7D58F12A75}">
       <text>
         <r>
           <rPr>
@@ -283,7 +273,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">【字段名】：
@@ -305,7 +294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{6E11A721-B664-40D3-85DD-BC88155953E5}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{DF491090-D29D-4744-9490-20E19292F9C4}">
       <text>
         <r>
           <rPr>
@@ -313,7 +302,6 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -332,7 +320,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="261">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1275,14 +1263,6 @@
   </si>
   <si>
     <t>当前经验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经验上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpMax</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1329,7 +1309,6 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1879,7 +1858,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{100E7CEC-1A4F-420D-BB6B-A17035948EBB}" name="Cfg_Property" displayName="Cfg_Property" ref="A1:N68" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{100E7CEC-1A4F-420D-BB6B-A17035948EBB}" name="Cfg_Property" displayName="Cfg_Property" ref="A1:N67" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <tableColumns count="14">
     <tableColumn id="9" xr3:uid="{3B8FC0A5-6EC5-4336-9DE8-86D6A6C0810E}" name="索引" dataDxfId="20"/>
     <tableColumn id="1" xr3:uid="{D2FC6B4B-167C-4D9F-B48B-BAE0E7C444DF}" name="id" dataDxfId="19"/>
@@ -2218,26 +2197,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.21875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>175</v>
       </c>
@@ -2281,7 +2260,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>191</v>
       </c>
@@ -2292,7 +2271,7 @@
       <c r="K2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>244</v>
       </c>
@@ -2303,7 +2282,7 @@
       <c r="K3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>191</v>
       </c>
@@ -2314,7 +2293,7 @@
       <c r="K4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>192</v>
       </c>
@@ -2338,7 +2317,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>193</v>
       </c>
@@ -2362,7 +2341,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>194</v>
       </c>
@@ -2394,7 +2373,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>195</v>
       </c>
@@ -2426,7 +2405,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>196</v>
       </c>
@@ -2450,7 +2429,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>197</v>
       </c>
@@ -2474,7 +2453,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>198</v>
       </c>
@@ -2498,7 +2477,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>199</v>
       </c>
@@ -2531,7 +2510,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>200</v>
       </c>
@@ -2561,7 +2540,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>201</v>
       </c>
@@ -2594,7 +2573,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>202</v>
       </c>
@@ -2618,7 +2597,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>203</v>
       </c>
@@ -2642,7 +2621,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>204</v>
       </c>
@@ -2666,7 +2645,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>205</v>
       </c>
@@ -2696,7 +2675,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>206</v>
       </c>
@@ -2726,7 +2705,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>207</v>
       </c>
@@ -2750,7 +2729,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>208</v>
       </c>
@@ -2774,7 +2753,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>209</v>
       </c>
@@ -2798,7 +2777,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>210</v>
       </c>
@@ -2822,7 +2801,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>211</v>
       </c>
@@ -2852,7 +2831,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>212</v>
       </c>
@@ -2876,7 +2855,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>213</v>
       </c>
@@ -2906,7 +2885,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>214</v>
       </c>
@@ -2930,7 +2909,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>215</v>
       </c>
@@ -2960,7 +2939,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>216</v>
       </c>
@@ -2984,7 +2963,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>217</v>
       </c>
@@ -3014,7 +2993,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>218</v>
       </c>
@@ -3038,7 +3017,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>219</v>
       </c>
@@ -3068,7 +3047,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>220</v>
       </c>
@@ -3092,7 +3071,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>221</v>
       </c>
@@ -3122,7 +3101,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>222</v>
       </c>
@@ -3146,7 +3125,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>223</v>
       </c>
@@ -3176,7 +3155,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>224</v>
       </c>
@@ -3206,7 +3185,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>225</v>
       </c>
@@ -3239,7 +3218,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>226</v>
       </c>
@@ -3272,7 +3251,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>227</v>
       </c>
@@ -3302,7 +3281,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>228</v>
       </c>
@@ -3332,7 +3311,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>229</v>
       </c>
@@ -3365,7 +3344,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>230</v>
       </c>
@@ -3398,7 +3377,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>231</v>
       </c>
@@ -3428,7 +3407,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>232</v>
       </c>
@@ -3458,7 +3437,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>233</v>
       </c>
@@ -3491,7 +3470,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>119</v>
       </c>
@@ -3524,7 +3503,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>234</v>
       </c>
@@ -3554,7 +3533,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>235</v>
       </c>
@@ -3584,7 +3563,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>236</v>
       </c>
@@ -3617,7 +3596,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>122</v>
       </c>
@@ -3650,7 +3629,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>237</v>
       </c>
@@ -3680,7 +3659,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>238</v>
       </c>
@@ -3710,7 +3689,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>239</v>
       </c>
@@ -3743,7 +3722,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>125</v>
       </c>
@@ -3776,7 +3755,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>240</v>
       </c>
@@ -3806,7 +3785,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>241</v>
       </c>
@@ -3836,7 +3815,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>242</v>
       </c>
@@ -3869,7 +3848,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>128</v>
       </c>
@@ -3902,7 +3881,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>243</v>
       </c>
@@ -3932,7 +3911,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>245</v>
       </c>
@@ -3950,7 +3929,7 @@
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
     </row>
-    <row r="62" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>246</v>
       </c>
@@ -3968,7 +3947,7 @@
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
     </row>
-    <row r="63" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>245</v>
       </c>
@@ -3986,7 +3965,7 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
     </row>
-    <row r="64" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>247</v>
       </c>
@@ -4021,7 +4000,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>257</v>
       </c>
@@ -4032,7 +4011,7 @@
         <v>178</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>248</v>
@@ -4046,90 +4025,62 @@
         <v>248</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B66" s="1">
-        <v>10002</v>
+        <v>10010</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>178</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G66" s="1">
         <v>100</v>
       </c>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
+      <c r="K66" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="M66" s="2"/>
       <c r="N66" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B67" s="1">
-        <v>10010</v>
+        <v>10011</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>178</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G67" s="1">
         <v>100</v>
       </c>
-      <c r="K67" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="K67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B68" s="1">
-        <v>10011</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="G68" s="1">
-        <v>100</v>
-      </c>
-      <c r="K68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="1" t="s">
         <v>251</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K68 M2:M68" xr:uid="{11F726DE-414D-4E38-91AF-619AA5CC235A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K67 M2:M67" xr:uid="{11F726DE-414D-4E38-91AF-619AA5CC235A}">
       <formula1>"成功,失败,设置为限制"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4145,10 +4096,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE678690-F593-430F-863F-9C7548EB1957}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -4173,10 +4124,10 @@
         <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>184</v>
@@ -4207,10 +4158,10 @@
         <v>253</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>178</v>

--- a/Doc/导出配置/Property.xlsx
+++ b/Doc/导出配置/Property.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D8971D-9500-4918-BD3F-3A33BE54E129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760EE9A4-F0DD-4B07-A147-220BB7B869A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Property" sheetId="1" r:id="rId1"/>
-    <sheet name="属性代码生成辅助" sheetId="3" r:id="rId2"/>
+    <sheet name="属性组类" sheetId="3" r:id="rId2"/>
+    <sheet name="属性组实例" sheetId="5" r:id="rId3"/>
+    <sheet name="对象代码生成辅助" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,10 +30,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{535E16FE-F9D1-4379-B289-45475BD76D47}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{D917225A-64F7-4614-8614-FEA81B8BAB1A}">
       <text>
         <r>
           <rPr>
@@ -52,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{6AC236AF-626A-45A4-8668-9D4295DE37B4}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{80CEF545-A177-4E47-8E46-50E6AE8C7909}">
       <text>
         <r>
           <rPr>
@@ -73,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{104C4A92-F3EC-46D7-B534-FFE87E09B7E2}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{FFAE9607-BBCC-40B0-96BF-C8E8103C2981}">
       <text>
         <r>
           <rPr>
@@ -94,7 +96,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{C42884F1-81AA-453A-ABB4-5314744E0D05}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B574A959-03EC-4B45-BAA3-EADCD8CEFF8C}">
       <text>
         <r>
           <rPr>
@@ -115,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{E5782A8D-40AE-4688-BD9F-90B0A7679BE3}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{D7951092-AB32-48EA-BD9C-4A14E0D689D5}">
       <text>
         <r>
           <rPr>
@@ -138,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{DDAEF253-F36A-435B-8186-041D9D643D2C}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{EC96BDD9-0CDE-4E50-B470-EB34608709A9}">
       <text>
         <r>
           <rPr>
@@ -163,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{5172AE4C-84F6-4977-9DD4-839ECB2375C9}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{FA263774-77F8-4D33-B2D7-22D7CA16AC49}">
       <text>
         <r>
           <rPr>
@@ -192,7 +194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{446BDA3C-772B-4575-B8D0-8180CD7C1323}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{0DC3347B-EA3B-4B15-9861-3629C9D3DF0A}">
       <text>
         <r>
           <rPr>
@@ -215,7 +217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{14A0C3AF-459C-430F-8A00-8FA8545B232F}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{F124117C-EC6B-437F-8DDD-A4354F5D6FD2}">
       <text>
         <r>
           <rPr>
@@ -244,7 +246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{C84B1BC0-BFF0-4871-AA07-901CF64EA536}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{5350DC02-5A22-4D19-A4D9-3480281B200B}">
       <text>
         <r>
           <rPr>
@@ -265,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{30EF11FE-175F-481D-B621-8C7D58F12A75}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{917F3A9A-B5BF-402A-AB04-C48325FA71F3}">
       <text>
         <r>
           <rPr>
@@ -294,7 +296,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{DF491090-D29D-4744-9490-20E19292F9C4}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{136CB90C-DC51-4B73-B86C-7D709D9F12B8}">
       <text>
         <r>
           <rPr>
@@ -320,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="306">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1033,10 +1035,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Battle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>说明</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1274,8 +1272,184 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Fight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>对象名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嵌套对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嵌套属性组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色初始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色初始|角色等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DU_PlayerLevel</t>
+  </si>
+  <si>
+    <t>DU_PlayerLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DU_PlayerInit</t>
+  </si>
+  <si>
+    <t>DU_PlayerInit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DU_Player</t>
+  </si>
+  <si>
+    <t>DU_Player</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性</t>
+  </si>
+  <si>
+    <t>战斗属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性|角色其他属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FightingUnit</t>
+  </si>
+  <si>
+    <t>角色其他属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性组名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战时属性</t>
+  </si>
+  <si>
+    <t>战时属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战时属性|战斗属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变量名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>public</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>protected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m_BattlePropertys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属属性类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FightingPropertys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerPros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FightingUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否声明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FightPros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattlePros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerInit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色经济属性</t>
+  </si>
+  <si>
+    <t>角色属性结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色初始属性结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色等级属性结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗对象属性结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始化类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性1，初始化时取的是属性表中的初始化数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始化</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1520,321 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="41">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1858,29 +2346,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{100E7CEC-1A4F-420D-BB6B-A17035948EBB}" name="Cfg_Property" displayName="Cfg_Property" ref="A1:N67" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{100E7CEC-1A4F-420D-BB6B-A17035948EBB}" name="Cfg_Property" displayName="Cfg_Property" ref="A1:N67" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <tableColumns count="14">
-    <tableColumn id="9" xr3:uid="{3B8FC0A5-6EC5-4336-9DE8-86D6A6C0810E}" name="索引" dataDxfId="20"/>
-    <tableColumn id="1" xr3:uid="{D2FC6B4B-167C-4D9F-B48B-BAE0E7C444DF}" name="id" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{20484817-2F7B-401F-8704-0806FEF34864}" name="分组" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{148AAF50-6A90-4D77-975D-AB72C9AFC2AE}" name="枚举名称" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{AE80ADAC-C7BC-4C90-AC4D-0BEBDC113A66}" name="显示名称" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{71BC1DB2-3212-4E16-9DA1-CAC4E9A2C703}" name="显示颜色" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{8FC3DA60-6EB6-4A41-92F4-64A603771123}" name="初始化值" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{A8DFE4DC-904B-4A48-B0DE-02121CDF601A}" name="显示生效值" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{3D21E091-3B8A-4981-B66D-61F08BF9B26E}" name="显示格式" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{1F161CC3-AE6E-44AA-A037-5BC87DB68766}" name="下限" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{5A8819C0-D545-4145-AD31-8C5065653BF2}" name="超下限处理" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{B7EF07F4-8703-4CC1-A643-BEAF7A9C5FA0}" name="上限" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{50798A1B-D983-4C28-B229-FDAED6D7A07D}" name="超上限处理" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{C5668DDF-9894-4882-8255-FDABFC97BF72}" name="属性描述" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{3B8FC0A5-6EC5-4336-9DE8-86D6A6C0810E}" name="索引" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{D2FC6B4B-167C-4D9F-B48B-BAE0E7C444DF}" name="id" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{20484817-2F7B-401F-8704-0806FEF34864}" name="分组" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{148AAF50-6A90-4D77-975D-AB72C9AFC2AE}" name="枚举名称" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{AE80ADAC-C7BC-4C90-AC4D-0BEBDC113A66}" name="显示名称" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{71BC1DB2-3212-4E16-9DA1-CAC4E9A2C703}" name="显示颜色" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{8FC3DA60-6EB6-4A41-92F4-64A603771123}" name="初始化值" dataDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{A8DFE4DC-904B-4A48-B0DE-02121CDF601A}" name="显示生效值" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{3D21E091-3B8A-4981-B66D-61F08BF9B26E}" name="显示格式" dataDxfId="30"/>
+    <tableColumn id="12" xr3:uid="{1F161CC3-AE6E-44AA-A037-5BC87DB68766}" name="下限" dataDxfId="29"/>
+    <tableColumn id="13" xr3:uid="{5A8819C0-D545-4145-AD31-8C5065653BF2}" name="超下限处理" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{B7EF07F4-8703-4CC1-A643-BEAF7A9C5FA0}" name="上限" dataDxfId="27"/>
+    <tableColumn id="14" xr3:uid="{50798A1B-D983-4C28-B229-FDAED6D7A07D}" name="超上限处理" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{C5668DDF-9894-4882-8255-FDABFC97BF72}" name="属性描述" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}" name="辅助_属性分组" displayName="辅助_属性分组" ref="A1:E4" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}" name="辅助_属性分组" displayName="辅助_属性分组" ref="A1:E4" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="A1:E4" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1889,11 +2377,59 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5D6A6F7-AAEC-489A-A982-D454642B9FB1}" name="索引" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{64C8F804-50F6-453C-95D2-735F62062283}" name="类名" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{9D653032-0D75-4239-958F-585FB5B3B1A7}" name="文件名" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{880DFEEF-A9D1-4BEB-8228-F611FA9F52BE}" name="数据分组" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{9F3931FC-0C41-47C2-A9BF-7D7FCD2BDFD8}" name="说明" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B5D6A6F7-AAEC-489A-A982-D454642B9FB1}" name="索引" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{64C8F804-50F6-453C-95D2-735F62062283}" name="类名" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{9D653032-0D75-4239-958F-585FB5B3B1A7}" name="文件名" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{880DFEEF-A9D1-4BEB-8228-F611FA9F52BE}" name="数据分组" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{9F3931FC-0C41-47C2-A9BF-7D7FCD2BDFD8}" name="说明" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3CCAA9EB-5BD1-48E4-BD1F-D69AF0AC8CB5}" name="辅助_属性组实例" displayName="辅助_属性组实例" ref="A1:G5" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A1:G5" xr:uid="{3CCAA9EB-5BD1-48E4-BD1F-D69AF0AC8CB5}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{1D5E3BC0-14E8-4883-8F06-CBBF0661EED6}" name="属性组名称" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{325DDF97-3B50-4BE2-90F1-8237B3A7AC58}" name="所属属性类型" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{33AA20B1-E876-443E-9504-E946FB0ADFE2}" name="变量名" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{F96BF0E0-3AFC-442D-935E-235D6F371D2E}" name="类型" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{A2A332DF-EB64-48AA-978F-11B61A70F4E4}" name="是否声明" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{F0267BD1-A2A6-4573-9FE2-031137BBEF3E}" name="说明" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{9721FE61-FB3D-447A-BC84-8658A18BA653}" name="初始化类型" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}" name="辅助_对象结构" displayName="辅助_对象结构" ref="A1:G5" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:G5" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{1B0643BF-BB28-46ED-8069-E16AFD579AC6}" name="对象名称" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{5A0FEDCE-970B-462D-B8FD-23575C30339E}" name="类名" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{B725040F-4F6F-415B-A398-9329A76CC585}" name="文件名" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{5AF54BAC-A50A-42B0-89AC-C59C685AB57D}" name="变量名" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D5E35CCB-39C5-4710-810E-3ED5F9B57288}" name="嵌套对象" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{DBAFCC1B-4764-4484-A586-729E4943A892}" name="嵌套属性组" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{219329F8-C801-42C4-908B-02F97609DB09}" name="说明" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2198,25 +2734,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>175</v>
       </c>
@@ -2260,9 +2796,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2" s="2"/>
       <c r="H2" s="2"/>
@@ -2271,9 +2807,9 @@
       <c r="K2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C3" s="2"/>
       <c r="H3" s="2"/>
@@ -2282,9 +2818,9 @@
       <c r="K3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C4" s="2"/>
       <c r="H4" s="2"/>
@@ -2293,9 +2829,9 @@
       <c r="K4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -2317,9 +2853,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -2341,9 +2877,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
@@ -2373,9 +2909,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B8" s="1">
         <v>11</v>
@@ -2396,7 +2932,7 @@
         <v>8000</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>181</v>
@@ -2405,9 +2941,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B9" s="1">
         <v>100</v>
@@ -2429,9 +2965,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B10" s="1">
         <v>101</v>
@@ -2453,9 +2989,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="1">
         <v>103</v>
@@ -2477,9 +3013,9 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B12" s="1">
         <v>104</v>
@@ -2510,9 +3046,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B13" s="1">
         <v>105</v>
@@ -2540,9 +3076,9 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B14" s="1">
         <v>106</v>
@@ -2573,9 +3109,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B15" s="1">
         <v>107</v>
@@ -2597,9 +3133,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B16" s="1">
         <v>200</v>
@@ -2621,9 +3157,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B17" s="1">
         <v>201</v>
@@ -2645,9 +3181,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B18" s="1">
         <v>202</v>
@@ -2675,9 +3211,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B19" s="1">
         <v>203</v>
@@ -2705,9 +3241,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" s="1">
         <v>300</v>
@@ -2729,9 +3265,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B21" s="1">
         <v>301</v>
@@ -2753,9 +3289,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B22" s="1">
         <v>400</v>
@@ -2777,9 +3313,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B23" s="1">
         <v>401</v>
@@ -2801,9 +3337,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B24" s="1">
         <v>402</v>
@@ -2831,9 +3367,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B25" s="1">
         <v>500</v>
@@ -2855,9 +3391,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B26" s="1">
         <v>501</v>
@@ -2885,9 +3421,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B27" s="1">
         <v>502</v>
@@ -2909,9 +3445,9 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B28" s="1">
         <v>503</v>
@@ -2939,9 +3475,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B29" s="1">
         <v>508</v>
@@ -2963,9 +3499,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B30" s="1">
         <v>509</v>
@@ -2993,9 +3529,9 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B31" s="1">
         <v>510</v>
@@ -3017,9 +3553,9 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" s="1">
         <v>511</v>
@@ -3047,9 +3583,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B33" s="1">
         <v>600</v>
@@ -3071,9 +3607,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B34" s="1">
         <v>601</v>
@@ -3101,9 +3637,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1">
         <v>602</v>
@@ -3125,9 +3661,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B36" s="1">
         <v>603</v>
@@ -3155,9 +3691,9 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B37" s="1">
         <v>700</v>
@@ -3185,9 +3721,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B38" s="1">
         <v>701</v>
@@ -3218,9 +3754,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B39" s="1">
         <v>702</v>
@@ -3251,9 +3787,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B40" s="1">
         <v>703</v>
@@ -3281,9 +3817,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B41" s="1">
         <v>800</v>
@@ -3311,9 +3847,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B42" s="1">
         <v>801</v>
@@ -3344,9 +3880,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B43" s="1">
         <v>802</v>
@@ -3377,9 +3913,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B44" s="1">
         <v>803</v>
@@ -3407,9 +3943,9 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B45" s="1">
         <v>900</v>
@@ -3437,9 +3973,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B46" s="1">
         <v>901</v>
@@ -3470,7 +4006,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>119</v>
       </c>
@@ -3503,9 +4039,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B48" s="1">
         <v>903</v>
@@ -3533,9 +4069,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B49" s="1">
         <v>1000</v>
@@ -3563,9 +4099,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B50" s="1">
         <v>1001</v>
@@ -3596,7 +4132,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>122</v>
       </c>
@@ -3629,9 +4165,9 @@
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B52" s="1">
         <v>1003</v>
@@ -3659,9 +4195,9 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B53" s="1">
         <v>1100</v>
@@ -3689,9 +4225,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B54" s="1">
         <v>1101</v>
@@ -3722,7 +4258,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>125</v>
       </c>
@@ -3755,9 +4291,9 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B56" s="1">
         <v>1103</v>
@@ -3785,9 +4321,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B57" s="1">
         <v>1200</v>
@@ -3815,9 +4351,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B58" s="1">
         <v>1201</v>
@@ -3848,7 +4384,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>128</v>
       </c>
@@ -3881,9 +4417,9 @@
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B60" s="1">
         <v>1203</v>
@@ -3911,9 +4447,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3929,9 +4465,9 @@
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
     </row>
-    <row r="62" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3947,9 +4483,9 @@
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
     </row>
-    <row r="63" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3965,9 +4501,9 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
     </row>
-    <row r="64" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B64" s="1">
         <v>10000</v>
@@ -3976,10 +4512,10 @@
         <v>178</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -3997,12 +4533,12 @@
         <v>181</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B65" s="1">
         <v>10001</v>
@@ -4011,10 +4547,10 @@
         <v>178</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -4022,12 +4558,12 @@
       <c r="K65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B66" s="1">
         <v>10010</v>
@@ -4036,25 +4572,25 @@
         <v>178</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G66" s="1">
         <v>100</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>250</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="B67" s="1">
         <v>10011</v>
@@ -4063,10 +4599,10 @@
         <v>178</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G67" s="1">
         <v>100</v>
@@ -4074,7 +4610,7 @@
       <c r="K67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -4096,10 +4632,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE678690-F593-430F-863F-9C7548EB1957}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="83" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -4116,58 +4655,58 @@
         <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>279</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>184</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>294</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>186</v>
+        <v>294</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>185</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -4177,4 +4716,269 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B6C5EB-2023-4E64-8B4C-1E4F428B410F}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G5" xr:uid="{3EC79629-F538-4F2F-8213-3EE91DDEC531}">
+      <formula1>"初始化"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E5" xr:uid="{330D1442-843A-434C-B276-806681896AD6}">
+      <formula1>"否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D5" xr:uid="{2A4FB296-0B66-466E-B40A-BD508FB5991A}">
+      <formula1>"public,protected,private"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA31B102-9B23-4EE7-BFE4-292DCDC0D462}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="14.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Doc/导出配置/Property.xlsx
+++ b/Doc/导出配置/Property.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760EE9A4-F0DD-4B07-A147-220BB7B869A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C17E694-79E5-4D31-BC89-B9D528F4AE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Property" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{D917225A-64F7-4614-8614-FEA81B8BAB1A}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{FF94826A-3CC8-447A-8D07-90748148DFE2}">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{80CEF545-A177-4E47-8E46-50E6AE8C7909}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{FE686D80-09F5-43EC-AB84-E05A94D4BD6B}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{FFAE9607-BBCC-40B0-96BF-C8E8103C2981}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{7922F6B7-ADDD-4CCA-A6E4-52BEA2486346}">
       <text>
         <r>
           <rPr>
@@ -96,7 +96,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B574A959-03EC-4B45-BAA3-EADCD8CEFF8C}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{83410632-6A51-47DC-B613-98D39FFB92AB}">
       <text>
         <r>
           <rPr>
@@ -117,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{D7951092-AB32-48EA-BD9C-4A14E0D689D5}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{9CC2CB2E-1B0B-4045-BA77-2DAD648E4826}">
       <text>
         <r>
           <rPr>
@@ -140,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{EC96BDD9-0CDE-4E50-B470-EB34608709A9}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{5603BFF3-5807-4CC7-BEEA-4E27BBA8CD49}">
       <text>
         <r>
           <rPr>
@@ -165,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{FA263774-77F8-4D33-B2D7-22D7CA16AC49}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{A10522CD-8F15-4338-8FC1-CFB16970436B}">
       <text>
         <r>
           <rPr>
@@ -194,7 +194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{0DC3347B-EA3B-4B15-9861-3629C9D3DF0A}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{92B009EF-B9A7-44E4-B942-F6D1F3322F88}">
       <text>
         <r>
           <rPr>
@@ -217,7 +217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{F124117C-EC6B-437F-8DDD-A4354F5D6FD2}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{E086F736-C000-4879-8947-E5513CB88FCF}">
       <text>
         <r>
           <rPr>
@@ -246,7 +246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{5350DC02-5A22-4D19-A4D9-3480281B200B}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{F1C7B98C-B2AD-4A42-B5C6-D823431C0C17}">
       <text>
         <r>
           <rPr>
@@ -267,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{917F3A9A-B5BF-402A-AB04-C48325FA71F3}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{514F8E11-E733-4CE4-8FF2-30281EF11DBD}">
       <text>
         <r>
           <rPr>
@@ -296,7 +296,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{136CB90C-DC51-4B73-B86C-7D709D9F12B8}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{81342AC6-E0B9-4757-A09A-425C1E4F4BB4}">
       <text>
         <r>
           <rPr>
@@ -1019,10 +1019,6 @@
     <t>设置为限制</t>
   </si>
   <si>
-    <t>###.##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>全战斗属性|战斗中属性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1370,14 +1366,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>protected</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>m_BattlePropertys</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>所属属性类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1450,6 +1438,18 @@
   </si>
   <si>
     <t>初始化</t>
+  </si>
+  <si>
+    <t>BattlePropertys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1512,32 +1512,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="41">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1634,6 +1619,23 @@
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2405,14 +2407,14 @@
     <tableColumn id="3" xr3:uid="{F96BF0E0-3AFC-442D-935E-235D6F371D2E}" name="类型" dataDxfId="12"/>
     <tableColumn id="5" xr3:uid="{A2A332DF-EB64-48AA-978F-11B61A70F4E4}" name="是否声明" dataDxfId="11"/>
     <tableColumn id="6" xr3:uid="{F0267BD1-A2A6-4573-9FE2-031137BBEF3E}" name="说明" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{9721FE61-FB3D-447A-BC84-8658A18BA653}" name="初始化类型" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{9721FE61-FB3D-447A-BC84-8658A18BA653}" name="初始化类型" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}" name="辅助_对象结构" displayName="辅助_对象结构" ref="A1:G5" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}" name="辅助_对象结构" displayName="辅助_对象结构" ref="A1:G5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A1:G5" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2423,13 +2425,13 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1B0643BF-BB28-46ED-8069-E16AFD579AC6}" name="对象名称" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{5A0FEDCE-970B-462D-B8FD-23575C30339E}" name="类名" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{B725040F-4F6F-415B-A398-9329A76CC585}" name="文件名" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{5AF54BAC-A50A-42B0-89AC-C59C685AB57D}" name="变量名" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{D5E35CCB-39C5-4710-810E-3ED5F9B57288}" name="嵌套对象" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{DBAFCC1B-4764-4484-A586-729E4943A892}" name="嵌套属性组" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{219329F8-C801-42C4-908B-02F97609DB09}" name="说明" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{1B0643BF-BB28-46ED-8069-E16AFD579AC6}" name="对象名称" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{5A0FEDCE-970B-462D-B8FD-23575C30339E}" name="类名" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{B725040F-4F6F-415B-A398-9329A76CC585}" name="文件名" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{5AF54BAC-A50A-42B0-89AC-C59C685AB57D}" name="变量名" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{D5E35CCB-39C5-4710-810E-3ED5F9B57288}" name="嵌套对象" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{DBAFCC1B-4764-4484-A586-729E4943A892}" name="嵌套属性组" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{219329F8-C801-42C4-908B-02F97609DB09}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2798,7 +2800,7 @@
     </row>
     <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C2" s="2"/>
       <c r="H2" s="2"/>
@@ -2809,7 +2811,7 @@
     </row>
     <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C3" s="2"/>
       <c r="H3" s="2"/>
@@ -2820,7 +2822,7 @@
     </row>
     <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C4" s="2"/>
       <c r="H4" s="2"/>
@@ -2831,13 +2833,13 @@
     </row>
     <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -2855,13 +2857,13 @@
     </row>
     <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>8</v>
@@ -2879,13 +2881,13 @@
     </row>
     <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>147</v>
@@ -2911,13 +2913,13 @@
     </row>
     <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B8" s="1">
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>148</v>
@@ -2932,7 +2934,7 @@
         <v>8000</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>181</v>
@@ -2943,13 +2945,13 @@
     </row>
     <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B9" s="1">
         <v>100</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>10</v>
@@ -2967,13 +2969,13 @@
     </row>
     <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B10" s="1">
         <v>101</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>11</v>
@@ -2991,13 +2993,13 @@
     </row>
     <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B11" s="1">
         <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>9</v>
@@ -3015,13 +3017,13 @@
     </row>
     <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B12" s="1">
         <v>104</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>85</v>
@@ -3035,8 +3037,8 @@
       <c r="H12" s="1">
         <v>10000</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>182</v>
+      <c r="I12" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L12" s="1">
         <v>9000</v>
@@ -3048,13 +3050,13 @@
     </row>
     <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B13" s="1">
         <v>105</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>86</v>
@@ -3068,8 +3070,8 @@
       <c r="H13" s="1">
         <v>10000</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>182</v>
+      <c r="I13" s="4" t="s">
+        <v>305</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
@@ -3078,13 +3080,13 @@
     </row>
     <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B14" s="1">
         <v>106</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>72</v>
@@ -3098,8 +3100,8 @@
       <c r="H14" s="1">
         <v>10000</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>182</v>
+      <c r="I14" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L14" s="1">
         <v>9000</v>
@@ -3111,13 +3113,13 @@
     </row>
     <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B15" s="1">
         <v>107</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>167</v>
@@ -3135,13 +3137,13 @@
     </row>
     <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B16" s="1">
         <v>200</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>20</v>
@@ -3159,13 +3161,13 @@
     </row>
     <row r="17" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" s="1">
         <v>201</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>21</v>
@@ -3183,13 +3185,13 @@
     </row>
     <row r="18" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B18" s="1">
         <v>202</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>25</v>
@@ -3203,8 +3205,8 @@
       <c r="H18" s="1">
         <v>10000</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>182</v>
+      <c r="I18" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1" t="s">
@@ -3213,13 +3215,13 @@
     </row>
     <row r="19" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B19" s="1">
         <v>203</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>26</v>
@@ -3233,8 +3235,8 @@
       <c r="H19" s="1">
         <v>10000</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>182</v>
+      <c r="I19" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1" t="s">
@@ -3243,13 +3245,13 @@
     </row>
     <row r="20" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B20" s="1">
         <v>300</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>28</v>
@@ -3267,13 +3269,13 @@
     </row>
     <row r="21" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" s="1">
         <v>301</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>29</v>
@@ -3291,13 +3293,13 @@
     </row>
     <row r="22" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B22" s="1">
         <v>400</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>30</v>
@@ -3315,13 +3317,13 @@
     </row>
     <row r="23" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B23" s="1">
         <v>401</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>31</v>
@@ -3339,13 +3341,13 @@
     </row>
     <row r="24" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B24" s="1">
         <v>402</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>32</v>
@@ -3359,8 +3361,8 @@
       <c r="H24" s="1">
         <v>10000</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>182</v>
+      <c r="I24" s="4" t="s">
+        <v>305</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1" t="s">
@@ -3369,13 +3371,13 @@
     </row>
     <row r="25" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B25" s="1">
         <v>500</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>35</v>
@@ -3393,13 +3395,13 @@
     </row>
     <row r="26" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B26" s="1">
         <v>501</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>36</v>
@@ -3413,8 +3415,8 @@
       <c r="H26" s="1">
         <v>10000</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>182</v>
+      <c r="I26" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1" t="s">
@@ -3423,13 +3425,13 @@
     </row>
     <row r="27" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B27" s="1">
         <v>502</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>38</v>
@@ -3447,13 +3449,13 @@
     </row>
     <row r="28" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B28" s="1">
         <v>503</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>39</v>
@@ -3467,8 +3469,8 @@
       <c r="H28" s="1">
         <v>10000</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>182</v>
+      <c r="I28" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1" t="s">
@@ -3477,13 +3479,13 @@
     </row>
     <row r="29" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B29" s="1">
         <v>508</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>40</v>
@@ -3501,13 +3503,13 @@
     </row>
     <row r="30" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B30" s="1">
         <v>509</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>41</v>
@@ -3521,8 +3523,8 @@
       <c r="H30" s="1">
         <v>10000</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>182</v>
+      <c r="I30" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1" t="s">
@@ -3531,13 +3533,13 @@
     </row>
     <row r="31" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B31" s="1">
         <v>510</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>43</v>
@@ -3555,13 +3557,13 @@
     </row>
     <row r="32" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B32" s="1">
         <v>511</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>44</v>
@@ -3575,8 +3577,8 @@
       <c r="H32" s="1">
         <v>10000</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>182</v>
+      <c r="I32" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1" t="s">
@@ -3585,13 +3587,13 @@
     </row>
     <row r="33" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" s="1">
         <v>600</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>47</v>
@@ -3609,13 +3611,13 @@
     </row>
     <row r="34" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B34" s="1">
         <v>601</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>48</v>
@@ -3629,8 +3631,8 @@
       <c r="H34" s="1">
         <v>10000</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>182</v>
+      <c r="I34" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1" t="s">
@@ -3639,13 +3641,13 @@
     </row>
     <row r="35" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B35" s="1">
         <v>602</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>49</v>
@@ -3663,13 +3665,13 @@
     </row>
     <row r="36" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B36" s="1">
         <v>603</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>50</v>
@@ -3683,8 +3685,8 @@
       <c r="H36" s="1">
         <v>10000</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>182</v>
+      <c r="I36" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1" t="s">
@@ -3693,13 +3695,13 @@
     </row>
     <row r="37" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B37" s="1">
         <v>700</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>154</v>
@@ -3713,8 +3715,8 @@
       <c r="H37" s="1">
         <v>10000</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>182</v>
+      <c r="I37" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1" t="s">
@@ -3723,13 +3725,13 @@
     </row>
     <row r="38" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B38" s="1">
         <v>701</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>15</v>
@@ -3743,8 +3745,8 @@
       <c r="H38" s="1">
         <v>10000</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>182</v>
+      <c r="I38" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L38" s="1">
         <v>7500</v>
@@ -3756,13 +3758,13 @@
     </row>
     <row r="39" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B39" s="1">
         <v>702</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>17</v>
@@ -3776,8 +3778,8 @@
       <c r="H39" s="1">
         <v>10000</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>182</v>
+      <c r="I39" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L39" s="1">
         <v>2000</v>
@@ -3789,13 +3791,13 @@
     </row>
     <row r="40" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B40" s="1">
         <v>703</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>18</v>
@@ -3809,8 +3811,8 @@
       <c r="H40" s="1">
         <v>10000</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>182</v>
+      <c r="I40" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1" t="s">
@@ -3819,13 +3821,13 @@
     </row>
     <row r="41" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B41" s="1">
         <v>800</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>51</v>
@@ -3839,8 +3841,8 @@
       <c r="H41" s="1">
         <v>10000</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>182</v>
+      <c r="I41" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1" t="s">
@@ -3849,13 +3851,13 @@
     </row>
     <row r="42" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B42" s="1">
         <v>801</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>52</v>
@@ -3869,8 +3871,8 @@
       <c r="H42" s="1">
         <v>10000</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>182</v>
+      <c r="I42" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L42" s="1">
         <v>7500</v>
@@ -3882,13 +3884,13 @@
     </row>
     <row r="43" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B43" s="1">
         <v>802</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>53</v>
@@ -3902,8 +3904,8 @@
       <c r="H43" s="1">
         <v>10000</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>182</v>
+      <c r="I43" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L43" s="1">
         <v>2000</v>
@@ -3915,13 +3917,13 @@
     </row>
     <row r="44" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B44" s="1">
         <v>803</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>54</v>
@@ -3935,8 +3937,8 @@
       <c r="H44" s="1">
         <v>10000</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>182</v>
+      <c r="I44" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
@@ -3945,13 +3947,13 @@
     </row>
     <row r="45" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B45" s="1">
         <v>900</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>55</v>
@@ -3965,8 +3967,8 @@
       <c r="H45" s="1">
         <v>10000</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>182</v>
+      <c r="I45" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
@@ -3975,13 +3977,13 @@
     </row>
     <row r="46" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B46" s="1">
         <v>901</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>56</v>
@@ -3995,8 +3997,8 @@
       <c r="H46" s="1">
         <v>10000</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>182</v>
+      <c r="I46" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L46" s="1">
         <v>7500</v>
@@ -4014,7 +4016,7 @@
         <v>902</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>57</v>
@@ -4028,8 +4030,8 @@
       <c r="H47" s="1">
         <v>10000</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>182</v>
+      <c r="I47" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L47" s="1">
         <v>2000</v>
@@ -4041,13 +4043,13 @@
     </row>
     <row r="48" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B48" s="1">
         <v>903</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>58</v>
@@ -4061,8 +4063,8 @@
       <c r="H48" s="1">
         <v>10000</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>182</v>
+      <c r="I48" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1" t="s">
@@ -4071,13 +4073,13 @@
     </row>
     <row r="49" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B49" s="1">
         <v>1000</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>59</v>
@@ -4091,8 +4093,8 @@
       <c r="H49" s="1">
         <v>10000</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>182</v>
+      <c r="I49" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1" t="s">
@@ -4101,13 +4103,13 @@
     </row>
     <row r="50" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B50" s="1">
         <v>1001</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>60</v>
@@ -4121,8 +4123,8 @@
       <c r="H50" s="1">
         <v>10000</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>182</v>
+      <c r="I50" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L50" s="1">
         <v>7500</v>
@@ -4140,7 +4142,7 @@
         <v>1002</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>61</v>
@@ -4154,8 +4156,8 @@
       <c r="H51" s="1">
         <v>10000</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>182</v>
+      <c r="I51" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L51" s="1">
         <v>2000</v>
@@ -4167,13 +4169,13 @@
     </row>
     <row r="52" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B52" s="1">
         <v>1003</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>62</v>
@@ -4187,8 +4189,8 @@
       <c r="H52" s="1">
         <v>10000</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>182</v>
+      <c r="I52" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1" t="s">
@@ -4197,13 +4199,13 @@
     </row>
     <row r="53" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B53" s="1">
         <v>1100</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>63</v>
@@ -4217,8 +4219,8 @@
       <c r="H53" s="1">
         <v>10000</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>182</v>
+      <c r="I53" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1" t="s">
@@ -4227,13 +4229,13 @@
     </row>
     <row r="54" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B54" s="1">
         <v>1101</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>64</v>
@@ -4247,8 +4249,8 @@
       <c r="H54" s="1">
         <v>10000</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>182</v>
+      <c r="I54" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L54" s="1">
         <v>7500</v>
@@ -4266,7 +4268,7 @@
         <v>1102</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>65</v>
@@ -4280,8 +4282,8 @@
       <c r="H55" s="1">
         <v>10000</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>182</v>
+      <c r="I55" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L55" s="1">
         <v>2000</v>
@@ -4293,13 +4295,13 @@
     </row>
     <row r="56" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B56" s="1">
         <v>1103</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>66</v>
@@ -4313,8 +4315,8 @@
       <c r="H56" s="1">
         <v>10000</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>182</v>
+      <c r="I56" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1" t="s">
@@ -4323,13 +4325,13 @@
     </row>
     <row r="57" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B57" s="1">
         <v>1200</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>67</v>
@@ -4343,8 +4345,8 @@
       <c r="H57" s="1">
         <v>10000</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>182</v>
+      <c r="I57" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1" t="s">
@@ -4353,13 +4355,13 @@
     </row>
     <row r="58" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B58" s="1">
         <v>1201</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>68</v>
@@ -4373,8 +4375,8 @@
       <c r="H58" s="1">
         <v>10000</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>182</v>
+      <c r="I58" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L58" s="1">
         <v>7500</v>
@@ -4392,7 +4394,7 @@
         <v>1202</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>69</v>
@@ -4406,8 +4408,8 @@
       <c r="H59" s="1">
         <v>10000</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>182</v>
+      <c r="I59" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="L59" s="1">
         <v>2000</v>
@@ -4419,13 +4421,13 @@
     </row>
     <row r="60" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B60" s="1">
         <v>1203</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>70</v>
@@ -4439,8 +4441,8 @@
       <c r="H60" s="1">
         <v>10000</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>182</v>
+      <c r="I60" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1" t="s">
@@ -4449,7 +4451,7 @@
     </row>
     <row r="61" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -4467,7 +4469,7 @@
     </row>
     <row r="62" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -4485,7 +4487,7 @@
     </row>
     <row r="63" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -4503,7 +4505,7 @@
     </row>
     <row r="64" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B64" s="1">
         <v>10000</v>
@@ -4512,10 +4514,10 @@
         <v>178</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -4533,12 +4535,12 @@
         <v>181</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B65" s="1">
         <v>10001</v>
@@ -4547,10 +4549,10 @@
         <v>178</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -4558,12 +4560,12 @@
       <c r="K65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B66" s="1">
         <v>10010</v>
@@ -4572,25 +4574,25 @@
         <v>178</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G66" s="1">
         <v>100</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B67" s="1">
         <v>10011</v>
@@ -4599,10 +4601,10 @@
         <v>178</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G67" s="1">
         <v>100</v>
@@ -4610,7 +4612,7 @@
       <c r="K67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4655,58 +4657,58 @@
         <v>177</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -4733,105 +4735,105 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -4869,7 +4871,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>174</v>
@@ -4878,99 +4880,99 @@
         <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/Doc/导出配置/Property.xlsx
+++ b/Doc/导出配置/Property.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C17E694-79E5-4D31-BC89-B9D528F4AE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E775CB-0C36-4C90-AD37-1921775D5597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Property" sheetId="1" r:id="rId1"/>
@@ -30,10 +30,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{FF94826A-3CC8-447A-8D07-90748148DFE2}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{BC8675FC-C098-4FE4-B1D9-BE0661A1E37A}">
       <text>
         <r>
           <rPr>
@@ -41,6 +41,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -54,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{FE686D80-09F5-43EC-AB84-E05A94D4BD6B}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{3D34ED72-21FB-4380-B6C6-0FCD9603F1AA}">
       <text>
         <r>
           <rPr>
@@ -62,6 +63,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -75,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{7922F6B7-ADDD-4CCA-A6E4-52BEA2486346}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{7E907A39-64B5-41C8-9852-F1098AE46484}">
       <text>
         <r>
           <rPr>
@@ -83,6 +85,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -96,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{83410632-6A51-47DC-B613-98D39FFB92AB}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{C1491D70-7216-4B4A-9FFE-A932BC6CAC21}">
       <text>
         <r>
           <rPr>
@@ -104,6 +107,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -117,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{9CC2CB2E-1B0B-4045-BA77-2DAD648E4826}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{67E8CA7C-6D2C-49F8-98BE-362B5689F063}">
       <text>
         <r>
           <rPr>
@@ -125,6 +129,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -140,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{5603BFF3-5807-4CC7-BEEA-4E27BBA8CD49}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{6A03BEF9-CA51-432C-B372-1E1AA7325AEC}">
       <text>
         <r>
           <rPr>
@@ -148,6 +153,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -165,7 +171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{A10522CD-8F15-4338-8FC1-CFB16970436B}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{D61A5215-0054-4388-AA9F-9D3384CDAE7C}">
       <text>
         <r>
           <rPr>
@@ -173,6 +179,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -194,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{92B009EF-B9A7-44E4-B942-F6D1F3322F88}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{4E52C0C5-16CD-421E-ABB1-9FC0698289BC}">
       <text>
         <r>
           <rPr>
@@ -202,6 +209,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -217,7 +225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{E086F736-C000-4879-8947-E5513CB88FCF}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{C90BAA09-04FB-4422-BE6B-2F6F010A72A5}">
       <text>
         <r>
           <rPr>
@@ -225,6 +233,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">【字段名】：
@@ -246,7 +255,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{F1C7B98C-B2AD-4A42-B5C6-D823431C0C17}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{F810637C-F94E-4555-9C6E-372BF0F35078}">
       <text>
         <r>
           <rPr>
@@ -254,6 +263,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -267,7 +277,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{514F8E11-E733-4CE4-8FF2-30281EF11DBD}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{7455842E-F838-46D3-A268-14D02EFA570C}">
       <text>
         <r>
           <rPr>
@@ -275,6 +285,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">【字段名】：
@@ -296,7 +307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{81342AC6-E0B9-4757-A09A-425C1E4F4BB4}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{98A84145-BC5C-45EB-B30A-7B3365DBD12F}">
       <text>
         <r>
           <rPr>
@@ -304,6 +315,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>【字段名】：
@@ -1483,6 +1495,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2736,25 +2749,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.21875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>175</v>
       </c>
@@ -2798,7 +2811,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>189</v>
       </c>
@@ -2809,7 +2822,7 @@
       <c r="K2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>242</v>
       </c>
@@ -2820,7 +2833,7 @@
       <c r="K3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>189</v>
       </c>
@@ -2831,7 +2844,7 @@
       <c r="K4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>190</v>
       </c>
@@ -2855,7 +2868,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>191</v>
       </c>
@@ -2879,7 +2892,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>192</v>
       </c>
@@ -2911,7 +2924,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>193</v>
       </c>
@@ -2943,7 +2956,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>194</v>
       </c>
@@ -2967,7 +2980,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>195</v>
       </c>
@@ -2991,7 +3004,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>196</v>
       </c>
@@ -3015,7 +3028,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>197</v>
       </c>
@@ -3048,7 +3061,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>198</v>
       </c>
@@ -3078,7 +3091,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>199</v>
       </c>
@@ -3111,7 +3124,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>200</v>
       </c>
@@ -3135,7 +3148,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>201</v>
       </c>
@@ -3159,7 +3172,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>202</v>
       </c>
@@ -3183,7 +3196,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>203</v>
       </c>
@@ -3213,7 +3226,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>204</v>
       </c>
@@ -3243,7 +3256,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>205</v>
       </c>
@@ -3267,7 +3280,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>206</v>
       </c>
@@ -3291,7 +3304,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>207</v>
       </c>
@@ -3315,7 +3328,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>208</v>
       </c>
@@ -3339,7 +3352,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>209</v>
       </c>
@@ -3369,7 +3382,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>210</v>
       </c>
@@ -3393,7 +3406,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>211</v>
       </c>
@@ -3423,7 +3436,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>212</v>
       </c>
@@ -3447,7 +3460,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>213</v>
       </c>
@@ -3477,7 +3490,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>214</v>
       </c>
@@ -3501,7 +3514,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>215</v>
       </c>
@@ -3531,7 +3544,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>216</v>
       </c>
@@ -3555,7 +3568,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>217</v>
       </c>
@@ -3585,7 +3598,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>218</v>
       </c>
@@ -3609,7 +3622,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>219</v>
       </c>
@@ -3639,7 +3652,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>220</v>
       </c>
@@ -3663,7 +3676,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>221</v>
       </c>
@@ -3693,7 +3706,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>222</v>
       </c>
@@ -3723,7 +3736,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>223</v>
       </c>
@@ -3756,7 +3769,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>224</v>
       </c>
@@ -3789,7 +3802,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>225</v>
       </c>
@@ -3819,7 +3832,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>226</v>
       </c>
@@ -3849,7 +3862,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>227</v>
       </c>
@@ -3882,7 +3895,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>228</v>
       </c>
@@ -3915,7 +3928,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>229</v>
       </c>
@@ -3945,7 +3958,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>230</v>
       </c>
@@ -3975,7 +3988,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>231</v>
       </c>
@@ -4008,7 +4021,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>119</v>
       </c>
@@ -4041,7 +4054,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>232</v>
       </c>
@@ -4071,7 +4084,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>233</v>
       </c>
@@ -4101,7 +4114,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>234</v>
       </c>
@@ -4134,7 +4147,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>122</v>
       </c>
@@ -4167,7 +4180,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>235</v>
       </c>
@@ -4197,7 +4210,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>236</v>
       </c>
@@ -4227,7 +4240,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>237</v>
       </c>
@@ -4260,7 +4273,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>125</v>
       </c>
@@ -4293,7 +4306,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>238</v>
       </c>
@@ -4323,7 +4336,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>239</v>
       </c>
@@ -4353,7 +4366,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>240</v>
       </c>
@@ -4386,7 +4399,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>128</v>
       </c>
@@ -4419,7 +4432,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>241</v>
       </c>
@@ -4449,7 +4462,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>243</v>
       </c>
@@ -4467,7 +4480,7 @@
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
     </row>
-    <row r="62" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>244</v>
       </c>
@@ -4485,7 +4498,7 @@
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
     </row>
-    <row r="63" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>243</v>
       </c>
@@ -4503,7 +4516,7 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
     </row>
-    <row r="64" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>245</v>
       </c>
@@ -4538,7 +4551,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>255</v>
       </c>
@@ -4563,7 +4576,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>253</v>
       </c>
@@ -4590,7 +4603,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>249</v>
       </c>
@@ -4634,13 +4647,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE678690-F593-430F-863F-9C7548EB1957}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.875" style="1"/>
+    <col min="4" max="4" width="9.875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="83" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="6" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -4723,14 +4736,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B6C5EB-2023-4E64-8B4C-1E4F428B410F}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.875" style="1"/>
+    <col min="7" max="7" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -4859,14 +4872,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA31B102-9B23-4EE7-BFE4-292DCDC0D462}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="14.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="14.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">

--- a/Doc/导出配置/Property.xlsx
+++ b/Doc/导出配置/Property.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E775CB-0C36-4C90-AD37-1921775D5597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACC5861-6DD5-42DE-9C41-B840CC28D7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Property" sheetId="1" r:id="rId1"/>
     <sheet name="属性组类" sheetId="3" r:id="rId2"/>
     <sheet name="属性组实例" sheetId="5" r:id="rId3"/>
-    <sheet name="对象代码生成辅助" sheetId="4" r:id="rId4"/>
+    <sheet name="对象类" sheetId="6" r:id="rId4"/>
+    <sheet name="对象实例" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,10 +31,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{BC8675FC-C098-4FE4-B1D9-BE0661A1E37A}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{0E955CE8-D051-4064-B29C-F8269BF504CB}">
       <text>
         <r>
           <rPr>
@@ -55,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{3D34ED72-21FB-4380-B6C6-0FCD9603F1AA}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{E1DAAC23-0F5A-4455-8D7A-2640E825E3DE}">
       <text>
         <r>
           <rPr>
@@ -77,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{7E907A39-64B5-41C8-9852-F1098AE46484}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{A5AD09C0-2119-4EF7-B0A4-FDFDFB090000}">
       <text>
         <r>
           <rPr>
@@ -99,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{C1491D70-7216-4B4A-9FFE-A932BC6CAC21}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{71EB0C47-214D-42C8-96E6-89697B0D75A3}">
       <text>
         <r>
           <rPr>
@@ -121,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{67E8CA7C-6D2C-49F8-98BE-362B5689F063}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{606A1B1B-D550-43D1-A5E5-A2C2E5172332}">
       <text>
         <r>
           <rPr>
@@ -145,7 +146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{6A03BEF9-CA51-432C-B372-1E1AA7325AEC}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{642596DF-3A21-4ECF-AB52-2E5EF118851F}">
       <text>
         <r>
           <rPr>
@@ -171,7 +172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{D61A5215-0054-4388-AA9F-9D3384CDAE7C}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{4DCF770A-6AA5-47E2-91FE-D96B69074DDB}">
       <text>
         <r>
           <rPr>
@@ -201,7 +202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{4E52C0C5-16CD-421E-ABB1-9FC0698289BC}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{853B81C3-A775-4F5D-9719-2100DEB559EB}">
       <text>
         <r>
           <rPr>
@@ -225,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{C90BAA09-04FB-4422-BE6B-2F6F010A72A5}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{E1C38145-C8AC-440F-9E8F-5ED377D22DC1}">
       <text>
         <r>
           <rPr>
@@ -255,7 +256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{F810637C-F94E-4555-9C6E-372BF0F35078}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{622C55FD-F62D-4B61-9A3E-AA920ED6C670}">
       <text>
         <r>
           <rPr>
@@ -277,7 +278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{7455842E-F838-46D3-A268-14D02EFA570C}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{972F2A37-0DBD-4E60-AE43-72CC5C0BE8C3}">
       <text>
         <r>
           <rPr>
@@ -307,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{98A84145-BC5C-45EB-B30A-7B3365DBD12F}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{F7F19A6E-16C7-46D2-8DBE-92D39DB4E5C6}">
       <text>
         <r>
           <rPr>
@@ -334,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="347">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1225,242 +1226,388 @@
     <t>####</t>
   </si>
   <si>
+    <t>等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnergyMax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前体力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrentEnergy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前经验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrentExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色初始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DU_PlayerLevel</t>
+  </si>
+  <si>
+    <t>DU_PlayerInit</t>
+  </si>
+  <si>
+    <t>DU_Player</t>
+  </si>
+  <si>
+    <t>战斗属性</t>
+  </si>
+  <si>
+    <t>战斗属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FightingUnit</t>
+  </si>
+  <si>
+    <t>角色其他属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性组名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战时属性</t>
+  </si>
+  <si>
+    <t>战时属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变量名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>public</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FightingPropertys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FightingUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否声明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FightPros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattlePros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerInit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始化类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性1，初始化时取的是属性表中的初始化数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始化</t>
+  </si>
+  <si>
+    <t>BattlePropertys</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#等级属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>#经济属性</t>
-  </si>
-  <si>
-    <t>等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体力上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnergyMax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色经济属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色身上的其他经济属性，例如等级，经验之类的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前体力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrentEnergy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前经验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrentExp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Player</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对象名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嵌套对象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嵌套属性组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>钻石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diamond</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经济属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyPros</t>
+  </si>
+  <si>
+    <t>CurrencyPros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OtherPros</t>
+  </si>
+  <si>
+    <t>OtherPros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特指等级和经验，包含升级的各种模板（自动、手动升级），消耗的内容使用其他东西替代等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钻石、金币等纯累积性的消耗数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力、经验获得提升等其他杂属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LvPros</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色等级</t>
+  </si>
+  <si>
+    <t>角色等级属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色其他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图点1</t>
+  </si>
+  <si>
+    <t>地图点1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性组类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象类</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>角色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>角色初始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色初始|角色等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DU_PlayerLevel</t>
-  </si>
-  <si>
-    <t>DU_PlayerLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DU_PlayerInit</t>
-  </si>
-  <si>
-    <t>DU_PlayerInit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DU_Player</t>
-  </si>
-  <si>
-    <t>DU_Player</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗属性</t>
-  </si>
-  <si>
-    <t>战斗属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗属性|角色其他属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FightingUnit</t>
-  </si>
-  <si>
-    <t>角色其他属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性组名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战时属性</t>
-  </si>
-  <si>
-    <t>战时属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>战斗对象</t>
+  </si>
+  <si>
+    <t>地图点</t>
+  </si>
+  <si>
+    <t>地图点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DU_MapPoint</t>
+  </si>
+  <si>
+    <t>DU_MapPoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DU_Group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图点组</t>
+  </si>
+  <si>
+    <t>地图点组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性|角色其他|角色货币</t>
+  </si>
+  <si>
+    <t>类约束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T2 : UnitBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;string , DU_MapPoint&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泛型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;T1,T2&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPointGroup</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>战时属性|战斗属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>变量名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>public</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属属性类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FightingPropertys</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlayerPros</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FightingUnit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否声明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FightPros</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattlePros</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlayerInit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlayerLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色经济属性</t>
+  </si>
+  <si>
+    <t>MapPoint1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明</t>
   </si>
   <si>
     <t>角色属性结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性1</t>
   </si>
   <si>
     <t>角色初始属性结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>角色等级属性结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>战斗对象属性结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始化类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗属性1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗属性1，初始化时取的是属性表中的初始化数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始化</t>
-  </si>
-  <si>
-    <t>BattlePropertys</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00</t>
+  </si>
+  <si>
+    <t>嵌套对象实例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嵌套属性组实例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色初始|角色等级|地图点组|地图点1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泛型参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗属性|角色等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1525,17 +1672,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="49">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1613,6 +1816,93 @@
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2361,30 +2651,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{100E7CEC-1A4F-420D-BB6B-A17035948EBB}" name="Cfg_Property" displayName="Cfg_Property" ref="A1:N67" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{100E7CEC-1A4F-420D-BB6B-A17035948EBB}" name="Cfg_Property" displayName="Cfg_Property" ref="A1:N75" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <tableColumns count="14">
-    <tableColumn id="9" xr3:uid="{3B8FC0A5-6EC5-4336-9DE8-86D6A6C0810E}" name="索引" dataDxfId="38"/>
-    <tableColumn id="1" xr3:uid="{D2FC6B4B-167C-4D9F-B48B-BAE0E7C444DF}" name="id" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{20484817-2F7B-401F-8704-0806FEF34864}" name="分组" dataDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{148AAF50-6A90-4D77-975D-AB72C9AFC2AE}" name="枚举名称" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{AE80ADAC-C7BC-4C90-AC4D-0BEBDC113A66}" name="显示名称" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{71BC1DB2-3212-4E16-9DA1-CAC4E9A2C703}" name="显示颜色" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{8FC3DA60-6EB6-4A41-92F4-64A603771123}" name="初始化值" dataDxfId="32"/>
-    <tableColumn id="11" xr3:uid="{A8DFE4DC-904B-4A48-B0DE-02121CDF601A}" name="显示生效值" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{3D21E091-3B8A-4981-B66D-61F08BF9B26E}" name="显示格式" dataDxfId="30"/>
-    <tableColumn id="12" xr3:uid="{1F161CC3-AE6E-44AA-A037-5BC87DB68766}" name="下限" dataDxfId="29"/>
-    <tableColumn id="13" xr3:uid="{5A8819C0-D545-4145-AD31-8C5065653BF2}" name="超下限处理" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{B7EF07F4-8703-4CC1-A643-BEAF7A9C5FA0}" name="上限" dataDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{50798A1B-D983-4C28-B229-FDAED6D7A07D}" name="超上限处理" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{C5668DDF-9894-4882-8255-FDABFC97BF72}" name="属性描述" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{3B8FC0A5-6EC5-4336-9DE8-86D6A6C0810E}" name="索引" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{D2FC6B4B-167C-4D9F-B48B-BAE0E7C444DF}" name="id" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{20484817-2F7B-401F-8704-0806FEF34864}" name="分组" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{148AAF50-6A90-4D77-975D-AB72C9AFC2AE}" name="枚举名称" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{AE80ADAC-C7BC-4C90-AC4D-0BEBDC113A66}" name="显示名称" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{71BC1DB2-3212-4E16-9DA1-CAC4E9A2C703}" name="显示颜色" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{8FC3DA60-6EB6-4A41-92F4-64A603771123}" name="初始化值" dataDxfId="40"/>
+    <tableColumn id="11" xr3:uid="{A8DFE4DC-904B-4A48-B0DE-02121CDF601A}" name="显示生效值" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{3D21E091-3B8A-4981-B66D-61F08BF9B26E}" name="显示格式" dataDxfId="38"/>
+    <tableColumn id="12" xr3:uid="{1F161CC3-AE6E-44AA-A037-5BC87DB68766}" name="下限" dataDxfId="37"/>
+    <tableColumn id="13" xr3:uid="{5A8819C0-D545-4145-AD31-8C5065653BF2}" name="超下限处理" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{B7EF07F4-8703-4CC1-A643-BEAF7A9C5FA0}" name="上限" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{50798A1B-D983-4C28-B229-FDAED6D7A07D}" name="超上限处理" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{C5668DDF-9894-4882-8255-FDABFC97BF72}" name="属性描述" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}" name="辅助_属性分组" displayName="辅助_属性分组" ref="A1:E4" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
-  <autoFilter ref="A1:E4" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}" name="辅助_属性分组" displayName="辅助_属性分组" ref="A1:E6" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+  <autoFilter ref="A1:E6" xr:uid="{874FB219-5240-44BD-A7B8-02AD6417982C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2392,19 +2682,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B5D6A6F7-AAEC-489A-A982-D454642B9FB1}" name="索引" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{64C8F804-50F6-453C-95D2-735F62062283}" name="类名" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{9D653032-0D75-4239-958F-585FB5B3B1A7}" name="文件名" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{880DFEEF-A9D1-4BEB-8228-F611FA9F52BE}" name="数据分组" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{9F3931FC-0C41-47C2-A9BF-7D7FCD2BDFD8}" name="说明" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{B5D6A6F7-AAEC-489A-A982-D454642B9FB1}" name="索引" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{64C8F804-50F6-453C-95D2-735F62062283}" name="类名" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{9D653032-0D75-4239-958F-585FB5B3B1A7}" name="文件名" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{880DFEEF-A9D1-4BEB-8228-F611FA9F52BE}" name="数据分组" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{9F3931FC-0C41-47C2-A9BF-7D7FCD2BDFD8}" name="说明" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3CCAA9EB-5BD1-48E4-BD1F-D69AF0AC8CB5}" name="辅助_属性组实例" displayName="辅助_属性组实例" ref="A1:G5" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:G5" xr:uid="{3CCAA9EB-5BD1-48E4-BD1F-D69AF0AC8CB5}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3CCAA9EB-5BD1-48E4-BD1F-D69AF0AC8CB5}" name="辅助_属性组实例" displayName="辅助_属性组实例" ref="A1:G7" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="A1:G7" xr:uid="{3CCAA9EB-5BD1-48E4-BD1F-D69AF0AC8CB5}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2414,21 +2704,21 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1D5E3BC0-14E8-4883-8F06-CBBF0661EED6}" name="属性组名称" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{325DDF97-3B50-4BE2-90F1-8237B3A7AC58}" name="所属属性类型" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{33AA20B1-E876-443E-9504-E946FB0ADFE2}" name="变量名" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{F96BF0E0-3AFC-442D-935E-235D6F371D2E}" name="类型" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{A2A332DF-EB64-48AA-978F-11B61A70F4E4}" name="是否声明" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{F0267BD1-A2A6-4573-9FE2-031137BBEF3E}" name="说明" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{9721FE61-FB3D-447A-BC84-8658A18BA653}" name="初始化类型" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{1D5E3BC0-14E8-4883-8F06-CBBF0661EED6}" name="属性组名称" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{325DDF97-3B50-4BE2-90F1-8237B3A7AC58}" name="属性组类" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{33AA20B1-E876-443E-9504-E946FB0ADFE2}" name="变量名" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{F96BF0E0-3AFC-442D-935E-235D6F371D2E}" name="类型" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{A2A332DF-EB64-48AA-978F-11B61A70F4E4}" name="是否声明" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{F0267BD1-A2A6-4573-9FE2-031137BBEF3E}" name="说明" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{9721FE61-FB3D-447A-BC84-8658A18BA653}" name="初始化类型" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}" name="辅助_对象结构" displayName="辅助_对象结构" ref="A1:G5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G5" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{977FD471-C383-40A2-BE31-73CCF0B10B07}" name="辅助_对象类" displayName="辅助_对象类" ref="A1:H7" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:H7" xr:uid="{977FD471-C383-40A2-BE31-73CCF0B10B07}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2436,15 +2726,37 @@
     <filterColumn colId="4" hiddenButton="1"/>
     <filterColumn colId="5" hiddenButton="1"/>
     <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1B0643BF-BB28-46ED-8069-E16AFD579AC6}" name="对象名称" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{5A0FEDCE-970B-462D-B8FD-23575C30339E}" name="类名" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{B725040F-4F6F-415B-A398-9329A76CC585}" name="文件名" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{5AF54BAC-A50A-42B0-89AC-C59C685AB57D}" name="变量名" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{D5E35CCB-39C5-4710-810E-3ED5F9B57288}" name="嵌套对象" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{DBAFCC1B-4764-4484-A586-729E4943A892}" name="嵌套属性组" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{219329F8-C801-42C4-908B-02F97609DB09}" name="说明" dataDxfId="0"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{05F690DE-629C-4ABE-B44E-5B983020652A}" name="索引" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{1689A8E1-DAFB-4BD2-93D3-B898942E5160}" name="文件名" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{3136513E-3379-4CFD-B41F-1E9690297848}" name="类名" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{423E2EC0-0B2E-4AEA-8BF3-600B49154C47}" name="泛型" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{584A99E7-A766-4D81-BADA-87B94772506F}" name="类约束" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{B71FD856-4CC0-4E70-8DF5-D0DEB90614B1}" name="嵌套对象实例" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{767D7354-20FA-439F-8F45-E2EBB2E15756}" name="嵌套属性组实例" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{50C5ADD7-1030-40BB-8FA3-66F6102D1A8F}" name="说明" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}" name="辅助_对象结构" displayName="辅助_对象结构" ref="A1:E7" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:E7" xr:uid="{AA22501A-E812-4F9D-A7C9-66B29AFCCA77}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{1B0643BF-BB28-46ED-8069-E16AFD579AC6}" name="对象名称" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{5A0FEDCE-970B-462D-B8FD-23575C30339E}" name="对象类" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{898EC82F-8141-48DB-BF25-C4FB37454724}" name="泛型参数" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{70E9505F-B7DC-4A98-A326-4C3B1CB08349}" name="变量名" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{AEB34080-0141-4915-BC1E-3D35175A12D8}" name="说明" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2748,26 +3060,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="1"/>
-    <col min="15" max="15" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>175</v>
       </c>
@@ -2811,7 +3123,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>189</v>
       </c>
@@ -2822,7 +3134,7 @@
       <c r="K2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>242</v>
       </c>
@@ -2833,7 +3145,7 @@
       <c r="K3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>189</v>
       </c>
@@ -2844,7 +3156,7 @@
       <c r="K4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>190</v>
       </c>
@@ -2868,7 +3180,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>191</v>
       </c>
@@ -2892,7 +3204,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>192</v>
       </c>
@@ -2924,7 +3236,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>193</v>
       </c>
@@ -2956,7 +3268,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>194</v>
       </c>
@@ -2980,7 +3292,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>195</v>
       </c>
@@ -3004,7 +3316,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>196</v>
       </c>
@@ -3028,7 +3340,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>197</v>
       </c>
@@ -3051,7 +3363,7 @@
         <v>10000</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L12" s="1">
         <v>9000</v>
@@ -3061,7 +3373,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>198</v>
       </c>
@@ -3084,14 +3396,14 @@
         <v>10000</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>199</v>
       </c>
@@ -3114,7 +3426,7 @@
         <v>10000</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L14" s="1">
         <v>9000</v>
@@ -3124,7 +3436,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>200</v>
       </c>
@@ -3148,7 +3460,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>201</v>
       </c>
@@ -3172,7 +3484,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>202</v>
       </c>
@@ -3196,7 +3508,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>203</v>
       </c>
@@ -3219,14 +3531,14 @@
         <v>10000</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>204</v>
       </c>
@@ -3249,14 +3561,14 @@
         <v>10000</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>205</v>
       </c>
@@ -3280,7 +3592,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>206</v>
       </c>
@@ -3304,7 +3616,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>207</v>
       </c>
@@ -3328,7 +3640,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>208</v>
       </c>
@@ -3352,7 +3664,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>209</v>
       </c>
@@ -3375,14 +3687,14 @@
         <v>10000</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>210</v>
       </c>
@@ -3406,7 +3718,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>211</v>
       </c>
@@ -3429,14 +3741,14 @@
         <v>10000</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>212</v>
       </c>
@@ -3460,7 +3772,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>213</v>
       </c>
@@ -3483,14 +3795,14 @@
         <v>10000</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>214</v>
       </c>
@@ -3514,7 +3826,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>215</v>
       </c>
@@ -3537,14 +3849,14 @@
         <v>10000</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>216</v>
       </c>
@@ -3568,7 +3880,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>217</v>
       </c>
@@ -3591,14 +3903,14 @@
         <v>10000</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>218</v>
       </c>
@@ -3622,7 +3934,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>219</v>
       </c>
@@ -3645,14 +3957,14 @@
         <v>10000</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>220</v>
       </c>
@@ -3676,7 +3988,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>221</v>
       </c>
@@ -3699,14 +4011,14 @@
         <v>10000</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>222</v>
       </c>
@@ -3729,14 +4041,14 @@
         <v>10000</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>223</v>
       </c>
@@ -3759,7 +4071,7 @@
         <v>10000</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L38" s="1">
         <v>7500</v>
@@ -3769,7 +4081,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>224</v>
       </c>
@@ -3792,7 +4104,7 @@
         <v>10000</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L39" s="1">
         <v>2000</v>
@@ -3802,7 +4114,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>225</v>
       </c>
@@ -3825,14 +4137,14 @@
         <v>10000</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>226</v>
       </c>
@@ -3855,14 +4167,14 @@
         <v>10000</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>227</v>
       </c>
@@ -3885,7 +4197,7 @@
         <v>10000</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L42" s="1">
         <v>7500</v>
@@ -3895,7 +4207,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>228</v>
       </c>
@@ -3918,7 +4230,7 @@
         <v>10000</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L43" s="1">
         <v>2000</v>
@@ -3928,7 +4240,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>229</v>
       </c>
@@ -3951,14 +4263,14 @@
         <v>10000</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>230</v>
       </c>
@@ -3981,14 +4293,14 @@
         <v>10000</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>231</v>
       </c>
@@ -4011,7 +4323,7 @@
         <v>10000</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L46" s="1">
         <v>7500</v>
@@ -4021,7 +4333,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>119</v>
       </c>
@@ -4044,7 +4356,7 @@
         <v>10000</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L47" s="1">
         <v>2000</v>
@@ -4054,7 +4366,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>232</v>
       </c>
@@ -4077,14 +4389,14 @@
         <v>10000</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>233</v>
       </c>
@@ -4107,14 +4419,14 @@
         <v>10000</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>234</v>
       </c>
@@ -4137,7 +4449,7 @@
         <v>10000</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L50" s="1">
         <v>7500</v>
@@ -4147,7 +4459,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>122</v>
       </c>
@@ -4170,7 +4482,7 @@
         <v>10000</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L51" s="1">
         <v>2000</v>
@@ -4180,7 +4492,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>235</v>
       </c>
@@ -4203,14 +4515,14 @@
         <v>10000</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>236</v>
       </c>
@@ -4233,14 +4545,14 @@
         <v>10000</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>237</v>
       </c>
@@ -4263,7 +4575,7 @@
         <v>10000</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L54" s="1">
         <v>7500</v>
@@ -4273,7 +4585,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>125</v>
       </c>
@@ -4296,7 +4608,7 @@
         <v>10000</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L55" s="1">
         <v>2000</v>
@@ -4306,7 +4618,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>238</v>
       </c>
@@ -4329,14 +4641,14 @@
         <v>10000</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>239</v>
       </c>
@@ -4359,14 +4671,14 @@
         <v>10000</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>240</v>
       </c>
@@ -4389,7 +4701,7 @@
         <v>10000</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L58" s="1">
         <v>7500</v>
@@ -4399,7 +4711,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>128</v>
       </c>
@@ -4422,7 +4734,7 @@
         <v>10000</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="L59" s="1">
         <v>2000</v>
@@ -4432,7 +4744,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>241</v>
       </c>
@@ -4455,14 +4767,14 @@
         <v>10000</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>243</v>
       </c>
@@ -4480,9 +4792,9 @@
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
     </row>
-    <row r="62" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -4498,7 +4810,7 @@
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
     </row>
-    <row r="63" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>243</v>
       </c>
@@ -4516,21 +4828,21 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
     </row>
-    <row r="64" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B64" s="1">
         <v>10000</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -4548,90 +4860,264 @@
         <v>181</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B65" s="1">
         <v>10001</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
       </c>
-      <c r="K65" s="2"/>
+      <c r="K65" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="M65" s="2"/>
       <c r="N65" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B66" s="1">
+        <v>243</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+    </row>
+    <row r="67" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+    </row>
+    <row r="68" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+    </row>
+    <row r="69" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" s="1">
         <v>10010</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="D69" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G69" s="1">
+        <v>100</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M69" s="2"/>
+      <c r="N69" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G66" s="1">
+      <c r="B70" s="1">
+        <v>10011</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G70" s="1">
         <v>100</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="K70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B71" s="5"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="5"/>
+    </row>
+    <row r="72" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" s="5"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="5"/>
+    </row>
+    <row r="73" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B73" s="5"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="5"/>
+    </row>
+    <row r="74" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B74" s="5">
+        <v>20000</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="M66" s="2"/>
-      <c r="N66" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A67" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B67" s="1">
-        <v>10011</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="G67" s="1">
-        <v>100</v>
-      </c>
-      <c r="K67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="1" t="s">
-        <v>249</v>
+      <c r="L74" s="5"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B75" s="5">
+        <v>20001</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L75" s="5"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="5" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K67 M2:M67" xr:uid="{11F726DE-414D-4E38-91AF-619AA5CC235A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M73 K2:K73" xr:uid="{11F726DE-414D-4E38-91AF-619AA5CC235A}">
       <formula1>"成功,失败,设置为限制"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4646,14 +5132,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE678690-F593-430F-863F-9C7548EB1957}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.875" style="1"/>
-    <col min="4" max="4" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="83" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.875" style="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -4675,13 +5161,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>183</v>
@@ -4692,13 +5178,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>184</v>
@@ -4709,19 +5195,53 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>252</v>
+      <c r="E5" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -4735,130 +5255,170 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B6C5EB-2023-4E64-8B4C-1E4F428B410F}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="8.875" style="1"/>
-    <col min="7" max="7" width="9.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>185</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>298</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>302</v>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G5" xr:uid="{3EC79629-F538-4F2F-8213-3EE91DDEC531}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G7" xr:uid="{3EC79629-F538-4F2F-8213-3EE91DDEC531}">
       <formula1>"初始化"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E5" xr:uid="{330D1442-843A-434C-B276-806681896AD6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E7" xr:uid="{330D1442-843A-434C-B276-806681896AD6}">
       <formula1>"否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D5" xr:uid="{2A4FB296-0B66-466E-B40A-BD508FB5991A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D7" xr:uid="{2A4FB296-0B66-466E-B40A-BD508FB5991A}">
       <formula1>"public,protected,private"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4870,122 +5430,286 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA31B102-9B23-4EE7-BFE4-292DCDC0D462}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93417A73-069C-4964-B06B-52BFA9C04B7B}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="14.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.875" style="1"/>
+    <col min="1" max="1" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA31B102-9B23-4EE7-BFE4-292DCDC0D462}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>298</v>
+      <c r="E5" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
